--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>HMY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -676,259 +676,285 @@
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42369</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42277</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42185</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1267200</v>
+        <v>1677200</v>
       </c>
       <c r="E8" s="3">
-        <v>1127400</v>
+        <v>1389000</v>
       </c>
       <c r="F8" s="3">
-        <v>1195900</v>
+        <v>1241800</v>
       </c>
       <c r="G8" s="3">
-        <v>1097500</v>
+        <v>1104900</v>
       </c>
       <c r="H8" s="3">
-        <v>1176100</v>
+        <v>1172000</v>
       </c>
       <c r="I8" s="3">
+        <v>1075500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1152600</v>
+      </c>
+      <c r="K8" s="3">
         <v>750100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>843200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>755500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>822800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>655200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>649600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>616000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>585000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>646000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>596800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>293200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>273400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1077000</v>
+        <v>1214000</v>
       </c>
       <c r="E9" s="3">
-        <v>1007100</v>
+        <v>1053800</v>
       </c>
       <c r="F9" s="3">
-        <v>1033900</v>
+        <v>1055400</v>
       </c>
       <c r="G9" s="3">
-        <v>940400</v>
+        <v>986900</v>
       </c>
       <c r="H9" s="3">
-        <v>917000</v>
+        <v>1013200</v>
       </c>
       <c r="I9" s="3">
+        <v>921600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>898600</v>
+      </c>
+      <c r="K9" s="3">
         <v>675300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>734000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>689200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>761800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>583700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>567700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>579700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>533800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>524900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>547700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>289500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>270700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>190200</v>
+        <v>463300</v>
       </c>
       <c r="E10" s="3">
-        <v>120300</v>
+        <v>335200</v>
       </c>
       <c r="F10" s="3">
-        <v>162000</v>
+        <v>186400</v>
       </c>
       <c r="G10" s="3">
-        <v>157100</v>
+        <v>117900</v>
       </c>
       <c r="H10" s="3">
-        <v>259200</v>
+        <v>158700</v>
       </c>
       <c r="I10" s="3">
+        <v>153900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>254000</v>
+      </c>
+      <c r="K10" s="3">
         <v>74700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>109200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>61000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>71600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>81900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>36300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>51200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>121100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>49100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -950,67 +976,75 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>8600</v>
+        <v>30600</v>
       </c>
       <c r="E12" s="3">
-        <v>6200</v>
+        <v>18600</v>
       </c>
       <c r="F12" s="3">
-        <v>5500</v>
+        <v>8400</v>
       </c>
       <c r="G12" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="H12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>6900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>6400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>8500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>5900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>7100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1068,67 +1102,79 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>37700</v>
+        <v>2900</v>
       </c>
       <c r="E14" s="3">
-        <v>229500</v>
+        <v>-33700</v>
       </c>
       <c r="F14" s="3">
-        <v>14900</v>
+        <v>36900</v>
       </c>
       <c r="G14" s="3">
-        <v>122500</v>
+        <v>224900</v>
       </c>
       <c r="H14" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I14" s="3">
+        <v>120000</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>225400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>329500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>13900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>114400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-1400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>249300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1186,8 +1232,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1206,126 +1258,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1133800</v>
+        <v>1273100</v>
       </c>
       <c r="E17" s="3">
-        <v>1259500</v>
+        <v>1152300</v>
       </c>
       <c r="F17" s="3">
-        <v>1104900</v>
+        <v>1111200</v>
       </c>
       <c r="G17" s="3">
-        <v>1096200</v>
+        <v>1234300</v>
       </c>
       <c r="H17" s="3">
-        <v>866300</v>
+        <v>1082800</v>
       </c>
       <c r="I17" s="3">
+        <v>1074300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>849000</v>
+      </c>
+      <c r="K17" s="3">
         <v>861100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>754200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>911200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>813500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1021500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>573700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>758500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>466400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>513000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>623000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>330900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>535400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>133300</v>
+        <v>404100</v>
       </c>
       <c r="E18" s="3">
-        <v>-132100</v>
+        <v>236700</v>
       </c>
       <c r="F18" s="3">
-        <v>91000</v>
+        <v>130600</v>
       </c>
       <c r="G18" s="3">
-        <v>1300</v>
+        <v>-129500</v>
       </c>
       <c r="H18" s="3">
-        <v>309800</v>
+        <v>89200</v>
       </c>
       <c r="I18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>303600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-111000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>89000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-155700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>9300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-366200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>75900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-142500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>118600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>133000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-37700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-262000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1347,149 +1413,163 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-4700</v>
+        <v>-2800</v>
       </c>
       <c r="E20" s="3">
-        <v>-8300</v>
+        <v>-10000</v>
       </c>
       <c r="F20" s="3">
-        <v>2500</v>
+        <v>-4600</v>
       </c>
       <c r="G20" s="3">
-        <v>-12300</v>
+        <v>-8200</v>
       </c>
       <c r="H20" s="3">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="I20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-7900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-9500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-7600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>6700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>223900</v>
+        <v>528400</v>
       </c>
       <c r="E21" s="3">
-        <v>-137000</v>
+        <v>224300</v>
       </c>
       <c r="F21" s="3">
-        <v>192000</v>
+        <v>219400</v>
       </c>
       <c r="G21" s="3">
+        <v>-134300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>188200</v>
+      </c>
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="H21" s="3">
-        <v>413800</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>405800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-126800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>186000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-165600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>128200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-365400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>165000</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3">
         <v>45400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-222400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3">
+        <v>6300</v>
+      </c>
       <c r="H22" s="3">
-        <v>6800</v>
+        <v>4100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
+      <c r="J22" s="3">
+        <v>6900</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
@@ -1497,11 +1577,11 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1524,126 +1604,144 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>128600</v>
+        <v>401300</v>
       </c>
       <c r="E23" s="3">
-        <v>-146900</v>
+        <v>226600</v>
       </c>
       <c r="F23" s="3">
-        <v>89200</v>
+        <v>126100</v>
       </c>
       <c r="G23" s="3">
-        <v>-11000</v>
+        <v>-143900</v>
       </c>
       <c r="H23" s="3">
-        <v>308000</v>
+        <v>87500</v>
       </c>
       <c r="I23" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>301900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-113500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>81100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-165200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-369400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>82600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-141700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>119300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>134500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-29000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-39200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-263000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>27200</v>
+        <v>83100</v>
       </c>
       <c r="E24" s="3">
-        <v>-15300</v>
+        <v>65300</v>
       </c>
       <c r="F24" s="3">
-        <v>12700</v>
+        <v>26700</v>
       </c>
       <c r="G24" s="3">
-        <v>26500</v>
+        <v>-14900</v>
       </c>
       <c r="H24" s="3">
-        <v>57400</v>
+        <v>12500</v>
       </c>
       <c r="I24" s="3">
+        <v>25900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>56300</v>
+      </c>
+      <c r="K24" s="3">
         <v>5300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-36700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>23600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-64500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>28100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>40900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-39800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1701,126 +1799,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>101400</v>
+        <v>318200</v>
       </c>
       <c r="E26" s="3">
-        <v>-131600</v>
+        <v>161300</v>
       </c>
       <c r="F26" s="3">
-        <v>76500</v>
+        <v>99400</v>
       </c>
       <c r="G26" s="3">
-        <v>-37500</v>
+        <v>-129000</v>
       </c>
       <c r="H26" s="3">
-        <v>250600</v>
+        <v>75000</v>
       </c>
       <c r="I26" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>245600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-118900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>72600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-154400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-332700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>59000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-77200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>91200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>93500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-30500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-36900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-223200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100200</v>
+        <v>316100</v>
       </c>
       <c r="E27" s="3">
-        <v>-132900</v>
+        <v>159200</v>
       </c>
       <c r="F27" s="3">
-        <v>75600</v>
+        <v>98200</v>
       </c>
       <c r="G27" s="3">
-        <v>-38000</v>
+        <v>-130200</v>
       </c>
       <c r="H27" s="3">
-        <v>249100</v>
+        <v>74100</v>
       </c>
       <c r="I27" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>244200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-120400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>72600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-154400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-332700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>59000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-77200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>91200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>93500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-30500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-36900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-223200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1878,8 +1994,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1937,8 +2059,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1996,8 +2124,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2055,126 +2189,144 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4700</v>
+        <v>2800</v>
       </c>
       <c r="E32" s="3">
-        <v>8300</v>
+        <v>10000</v>
       </c>
       <c r="F32" s="3">
-        <v>-2500</v>
+        <v>4600</v>
       </c>
       <c r="G32" s="3">
-        <v>12300</v>
+        <v>8200</v>
       </c>
       <c r="H32" s="3">
-        <v>-5000</v>
+        <v>-2400</v>
       </c>
       <c r="I32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>7900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>9500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>7600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-6700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100200</v>
+        <v>316100</v>
       </c>
       <c r="E33" s="3">
-        <v>-132900</v>
+        <v>159200</v>
       </c>
       <c r="F33" s="3">
-        <v>75600</v>
+        <v>98200</v>
       </c>
       <c r="G33" s="3">
-        <v>-38000</v>
+        <v>-130200</v>
       </c>
       <c r="H33" s="3">
-        <v>249100</v>
+        <v>74100</v>
       </c>
       <c r="I33" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>244200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-120400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>72600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-154400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-332700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>59000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-77200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>91200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>93500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-30500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-36900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-223200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2232,131 +2384,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100200</v>
+        <v>316100</v>
       </c>
       <c r="E35" s="3">
-        <v>-132900</v>
+        <v>159200</v>
       </c>
       <c r="F35" s="3">
-        <v>75600</v>
+        <v>98200</v>
       </c>
       <c r="G35" s="3">
-        <v>-38000</v>
+        <v>-130200</v>
       </c>
       <c r="H35" s="3">
-        <v>249100</v>
+        <v>74100</v>
       </c>
       <c r="I35" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>244200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-120400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>72600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-154400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-332700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>59000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-77200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>91200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>93500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-30500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-36900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-223200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42369</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42277</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42185</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2378,8 +2548,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2401,67 +2573,75 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>119600</v>
+        <v>183400</v>
       </c>
       <c r="E41" s="3">
-        <v>133400</v>
+        <v>153100</v>
       </c>
       <c r="F41" s="3">
-        <v>160200</v>
+        <v>117200</v>
       </c>
       <c r="G41" s="3">
-        <v>153600</v>
+        <v>130700</v>
       </c>
       <c r="H41" s="3">
-        <v>229700</v>
+        <v>157000</v>
       </c>
       <c r="I41" s="3">
+        <v>150500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>225100</v>
+      </c>
+      <c r="K41" s="3">
         <v>346300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>68100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>57200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>82800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>43700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>69400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>81700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>72000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>84300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>60000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>105300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>75600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2519,421 +2699,469 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>127000</v>
+        <v>175500</v>
       </c>
       <c r="E43" s="3">
-        <v>91600</v>
+        <v>127900</v>
       </c>
       <c r="F43" s="3">
-        <v>102600</v>
+        <v>124200</v>
       </c>
       <c r="G43" s="3">
-        <v>90000</v>
+        <v>89800</v>
       </c>
       <c r="H43" s="3">
-        <v>80900</v>
+        <v>100600</v>
       </c>
       <c r="I43" s="3">
+        <v>88200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>79300</v>
+      </c>
+      <c r="K43" s="3">
         <v>71300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>71400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>61300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>70900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>70600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>65300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>65800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>48600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>44300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>45900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>55400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>55000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>149500</v>
+        <v>171500</v>
       </c>
       <c r="E44" s="3">
-        <v>153500</v>
+        <v>174300</v>
       </c>
       <c r="F44" s="3">
-        <v>121500</v>
+        <v>146500</v>
       </c>
       <c r="G44" s="3">
-        <v>138500</v>
+        <v>150500</v>
       </c>
       <c r="H44" s="3">
-        <v>119800</v>
+        <v>119100</v>
       </c>
       <c r="I44" s="3">
+        <v>135700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>117400</v>
+      </c>
+      <c r="K44" s="3">
         <v>131900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>106400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>113200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>107100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>109000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>90100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>73900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>95800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>78300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>86400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>89400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>91500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19900</v>
+        <v>15100</v>
       </c>
       <c r="E45" s="3">
-        <v>29700</v>
+        <v>8100</v>
       </c>
       <c r="F45" s="3">
-        <v>36300</v>
+        <v>19500</v>
       </c>
       <c r="G45" s="3">
-        <v>83800</v>
+        <v>29200</v>
       </c>
       <c r="H45" s="3">
-        <v>43000</v>
+        <v>35600</v>
       </c>
       <c r="I45" s="3">
+        <v>82100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>42200</v>
+      </c>
+      <c r="K45" s="3">
         <v>4400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>32200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>20300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>14700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>35700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>107300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>102200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>90800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>25900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1100</v>
       </c>
       <c r="T45" s="3">
         <v>1100</v>
       </c>
       <c r="U45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>416100</v>
+        <v>545500</v>
       </c>
       <c r="E46" s="3">
-        <v>408300</v>
+        <v>463300</v>
       </c>
       <c r="F46" s="3">
-        <v>420600</v>
+        <v>407500</v>
       </c>
       <c r="G46" s="3">
-        <v>465900</v>
+        <v>400100</v>
       </c>
       <c r="H46" s="3">
-        <v>473500</v>
+        <v>412200</v>
       </c>
       <c r="I46" s="3">
+        <v>456500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>464000</v>
+      </c>
+      <c r="K46" s="3">
         <v>553800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>278100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>252000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>275600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>259000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>332100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>323500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>307200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>232800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>193400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>251300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>223200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>24100</v>
+        <v>23000</v>
       </c>
       <c r="E47" s="3">
-        <v>27200</v>
+        <v>23700</v>
       </c>
       <c r="F47" s="3">
-        <v>24200</v>
+        <v>23700</v>
       </c>
       <c r="G47" s="3">
-        <v>25000</v>
+        <v>26600</v>
       </c>
       <c r="H47" s="3">
-        <v>31500</v>
+        <v>23800</v>
       </c>
       <c r="I47" s="3">
+        <v>24500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K47" s="3">
         <v>29100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>25800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>25600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>39000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>21600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>21300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>15400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>11300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>11900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>6100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>6000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2120800</v>
+        <v>2269400</v>
       </c>
       <c r="E48" s="3">
-        <v>1790900</v>
+        <v>2216100</v>
       </c>
       <c r="F48" s="3">
-        <v>1948200</v>
+        <v>2045300</v>
       </c>
       <c r="G48" s="3">
-        <v>1830400</v>
+        <v>1755000</v>
       </c>
       <c r="H48" s="3">
-        <v>1884900</v>
+        <v>1909200</v>
       </c>
       <c r="I48" s="3">
+        <v>1793700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1847200</v>
+      </c>
+      <c r="K48" s="3">
         <v>1590100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1536800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1597500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1876300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1920500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2036200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1969700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1816300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2007600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2063100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2111000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2092600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>192100</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2200</v>
+        <v>1400</v>
       </c>
       <c r="E49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G49" s="3">
         <v>2600</v>
       </c>
-      <c r="F49" s="3">
-        <v>19000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>19900</v>
-      </c>
       <c r="H49" s="3">
-        <v>29500</v>
+        <v>18600</v>
       </c>
       <c r="I49" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>28900</v>
+      </c>
+      <c r="K49" s="3">
         <v>29200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>29100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>30700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>30700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>31900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>39500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>39500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>51200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>58400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>60200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>62500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>62700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2991,8 +3219,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3050,67 +3284,79 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>343100</v>
+        <v>352600</v>
       </c>
       <c r="E52" s="3">
-        <v>321200</v>
+        <v>351300</v>
       </c>
       <c r="F52" s="3">
-        <v>313900</v>
+        <v>336200</v>
       </c>
       <c r="G52" s="3">
-        <v>317700</v>
+        <v>314700</v>
       </c>
       <c r="H52" s="3">
-        <v>346000</v>
+        <v>307600</v>
       </c>
       <c r="I52" s="3">
+        <v>311400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>339100</v>
+      </c>
+      <c r="K52" s="3">
         <v>232600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>203300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>209200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>215600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>215500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>209700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>201000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>197000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>174100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>173100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>176800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>174800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3168,67 +3414,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2906200</v>
+        <v>3192000</v>
       </c>
       <c r="E54" s="3">
-        <v>2550100</v>
+        <v>3056000</v>
       </c>
       <c r="F54" s="3">
-        <v>2725900</v>
+        <v>2814700</v>
       </c>
       <c r="G54" s="3">
-        <v>2658800</v>
+        <v>2499100</v>
       </c>
       <c r="H54" s="3">
-        <v>2755400</v>
+        <v>2671400</v>
       </c>
       <c r="I54" s="3">
+        <v>2605600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>2700300</v>
+      </c>
+      <c r="K54" s="3">
         <v>2434800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2073200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2114900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2421700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2448400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2638800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2549200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2382900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2484700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2495800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2607500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2559200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>230400</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3250,8 +3508,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3273,176 +3533,190 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>249900</v>
+        <v>275500</v>
       </c>
       <c r="E57" s="3">
-        <v>244800</v>
+        <v>279700</v>
       </c>
       <c r="F57" s="3">
-        <v>228700</v>
+        <v>244900</v>
       </c>
       <c r="G57" s="3">
-        <v>239100</v>
+        <v>239900</v>
       </c>
       <c r="H57" s="3">
-        <v>213800</v>
+        <v>224100</v>
       </c>
       <c r="I57" s="3">
+        <v>234300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>209500</v>
+      </c>
+      <c r="K57" s="3">
         <v>163800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>159400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>165500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>175800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>167500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>148500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>131800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>125100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>113500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>112500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>129600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>117600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>5500</v>
       </c>
       <c r="F58" s="3">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>21100</v>
+        <v>1300</v>
       </c>
       <c r="H58" s="3">
-        <v>21200</v>
+        <v>20000</v>
       </c>
       <c r="I58" s="3">
+        <v>20700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K58" s="3">
         <v>13900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>42700</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>120200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>20100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>20500</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24500</v>
+        <v>61500</v>
       </c>
       <c r="E59" s="3">
-        <v>24800</v>
+        <v>81500</v>
       </c>
       <c r="F59" s="3">
-        <v>32300</v>
+        <v>24000</v>
       </c>
       <c r="G59" s="3">
-        <v>42300</v>
+        <v>24300</v>
       </c>
       <c r="H59" s="3">
-        <v>119400</v>
+        <v>31700</v>
       </c>
       <c r="I59" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>117000</v>
+      </c>
+      <c r="K59" s="3">
         <v>234200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>38500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>18100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3" t="s">
+      <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
@@ -3450,185 +3724,209 @@
       <c r="U59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>100</v>
+      </c>
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>274400</v>
+        <v>337700</v>
       </c>
       <c r="E60" s="3">
-        <v>271000</v>
+        <v>366600</v>
       </c>
       <c r="F60" s="3">
-        <v>281300</v>
+        <v>268900</v>
       </c>
       <c r="G60" s="3">
-        <v>302500</v>
+        <v>265600</v>
       </c>
       <c r="H60" s="3">
-        <v>354400</v>
+        <v>275700</v>
       </c>
       <c r="I60" s="3">
+        <v>296500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>347400</v>
+      </c>
+      <c r="K60" s="3">
         <v>411900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>202500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>186200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>199400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>223000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>150200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>252000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>129000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>136300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>133100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>129700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>117600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>376200</v>
+        <v>178700</v>
       </c>
       <c r="E61" s="3">
-        <v>173200</v>
+        <v>298600</v>
       </c>
       <c r="F61" s="3">
-        <v>173100</v>
+        <v>368700</v>
       </c>
       <c r="G61" s="3">
-        <v>162000</v>
+        <v>169800</v>
       </c>
       <c r="H61" s="3">
-        <v>240100</v>
+        <v>169700</v>
       </c>
       <c r="I61" s="3">
+        <v>158800</v>
+      </c>
+      <c r="J61" s="3">
+        <v>235300</v>
+      </c>
+      <c r="K61" s="3">
         <v>406600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>297100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>335400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>350300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>305000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>168800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>19600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>89200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>136800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>211900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>292400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>240700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>523700</v>
+        <v>541200</v>
       </c>
       <c r="E62" s="3">
-        <v>465000</v>
+        <v>528600</v>
       </c>
       <c r="F62" s="3">
-        <v>497900</v>
+        <v>479900</v>
       </c>
       <c r="G62" s="3">
-        <v>493700</v>
+        <v>455700</v>
       </c>
       <c r="H62" s="3">
-        <v>585900</v>
+        <v>488000</v>
       </c>
       <c r="I62" s="3">
+        <v>483800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>574200</v>
+      </c>
+      <c r="K62" s="3">
         <v>342900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>277400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>291400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>344900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>348000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>362800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>357200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>341500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>320800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>308500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>309400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>306200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>29200</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3686,8 +3984,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3745,8 +4049,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3804,67 +4114,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1179200</v>
+        <v>1065300</v>
       </c>
       <c r="E66" s="3">
-        <v>913600</v>
+        <v>1200400</v>
       </c>
       <c r="F66" s="3">
-        <v>955900</v>
+        <v>1122200</v>
       </c>
       <c r="G66" s="3">
-        <v>961200</v>
+        <v>895300</v>
       </c>
       <c r="H66" s="3">
-        <v>1134400</v>
+        <v>936800</v>
       </c>
       <c r="I66" s="3">
+        <v>942000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1111700</v>
+      </c>
+      <c r="K66" s="3">
         <v>1161600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>776700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>813000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>894600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>876000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>681800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>628900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>559600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>593900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>653500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>731500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>664600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3886,8 +4208,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3945,8 +4269,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4004,8 +4334,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4063,8 +4399,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4122,67 +4464,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-67200</v>
+        <v>368300</v>
       </c>
       <c r="E72" s="3">
-        <v>-157700</v>
+        <v>97300</v>
       </c>
       <c r="F72" s="3">
-        <v>-24200</v>
+        <v>-65800</v>
       </c>
       <c r="G72" s="3">
-        <v>-96600</v>
+        <v>-154600</v>
       </c>
       <c r="H72" s="3">
-        <v>-173400</v>
+        <v>-23800</v>
       </c>
       <c r="I72" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-169900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-521200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-313500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-399400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-236200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-245200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>92900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>62600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>143600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-10500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-99000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-129900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-111300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4240,8 +4594,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4299,8 +4659,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4358,67 +4724,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1727100</v>
+        <v>2126700</v>
       </c>
       <c r="E76" s="3">
-        <v>1636500</v>
+        <v>1855700</v>
       </c>
       <c r="F76" s="3">
-        <v>1770000</v>
+        <v>1692500</v>
       </c>
       <c r="G76" s="3">
-        <v>1697600</v>
+        <v>1603800</v>
       </c>
       <c r="H76" s="3">
-        <v>1620900</v>
+        <v>1734600</v>
       </c>
       <c r="I76" s="3">
+        <v>1663600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1588500</v>
+      </c>
+      <c r="K76" s="3">
         <v>1273300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1296500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1301900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1527100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1572400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1957000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1920300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1823300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1890800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1842300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1876000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1894600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4476,131 +4854,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42369</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42277</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42185</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100200</v>
+        <v>316100</v>
       </c>
       <c r="E81" s="3">
-        <v>-132900</v>
+        <v>159200</v>
       </c>
       <c r="F81" s="3">
-        <v>75600</v>
+        <v>98200</v>
       </c>
       <c r="G81" s="3">
-        <v>-38000</v>
+        <v>-130200</v>
       </c>
       <c r="H81" s="3">
-        <v>249100</v>
+        <v>74100</v>
       </c>
       <c r="I81" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>244200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-120400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>72600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-154400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-332700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>59000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-77200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>91200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>93500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-30500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-36900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-223200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4622,8 +5018,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4681,8 +5079,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4740,8 +5144,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4799,8 +5209,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4858,8 +5274,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4917,8 +5339,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4976,67 +5404,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>167000</v>
+        <v>373500</v>
       </c>
       <c r="E89" s="3">
-        <v>-1457700</v>
+        <v>367500</v>
       </c>
       <c r="F89" s="3">
-        <v>1834900</v>
+        <v>163600</v>
       </c>
       <c r="G89" s="3">
-        <v>185200</v>
+        <v>-1428600</v>
       </c>
       <c r="H89" s="3">
-        <v>314800</v>
+        <v>1798200</v>
       </c>
       <c r="I89" s="3">
+        <v>181500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>308500</v>
+      </c>
+      <c r="K89" s="3">
         <v>108400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>148900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>116800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>158100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>127100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>120500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>123900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>113500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>184600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>120800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>50900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>132800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5058,67 +5498,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3868000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3994000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3646000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3044000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3170000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2776000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2366000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1340000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2270000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-151700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-143200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-123700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-168700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-161000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-84900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-80100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-42100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-187500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5176,8 +5624,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5235,67 +5689,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-363900</v>
+        <v>-199000</v>
       </c>
       <c r="E94" s="3">
-        <v>1466600</v>
+        <v>-209100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1804400</v>
+        <v>-356600</v>
       </c>
       <c r="G94" s="3">
-        <v>-152200</v>
+        <v>1437300</v>
       </c>
       <c r="H94" s="3">
-        <v>-308900</v>
+        <v>-1768300</v>
       </c>
       <c r="I94" s="3">
+        <v>-149200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-302700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-72700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-121100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-141400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-139700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-340200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-170000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-158300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-57400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-96200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-79800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-42300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-192100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5317,25 +5783,27 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-7900</v>
+        <v>-25900</v>
       </c>
       <c r="E96" s="3">
-        <v>-14000</v>
+        <v>-500</v>
       </c>
       <c r="F96" s="3">
-        <v>-9400</v>
+        <v>-7700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-13700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-9200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -5353,20 +5821,20 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-10100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-14500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5376,8 +5844,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5435,8 +5909,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5494,8 +5974,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5553,181 +6039,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>181100</v>
+        <v>-146500</v>
       </c>
       <c r="E100" s="3">
-        <v>-38600</v>
+        <v>-113800</v>
       </c>
       <c r="F100" s="3">
-        <v>-24100</v>
+        <v>177500</v>
       </c>
       <c r="G100" s="3">
-        <v>-116300</v>
+        <v>-37900</v>
       </c>
       <c r="H100" s="3">
-        <v>-117900</v>
+        <v>-23600</v>
       </c>
       <c r="I100" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="K100" s="3">
         <v>250100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-15500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>20900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>196300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>36500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>31300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-62300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-56000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>21200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>12900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M101" s="3">
+        <v>200</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T101" s="3">
         <v>2000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F101" s="3">
-        <v>100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K101" s="3">
-        <v>200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>5100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>500</v>
       </c>
       <c r="U101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>500</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-13800</v>
+        <v>30400</v>
       </c>
       <c r="E102" s="3">
-        <v>-26800</v>
+        <v>35900</v>
       </c>
       <c r="F102" s="3">
-        <v>6600</v>
+        <v>-13500</v>
       </c>
       <c r="G102" s="3">
-        <v>-76200</v>
+        <v>-26300</v>
       </c>
       <c r="H102" s="3">
-        <v>-116600</v>
+        <v>6500</v>
       </c>
       <c r="I102" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-114300</v>
+      </c>
+      <c r="K102" s="3">
         <v>278200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>14000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-22700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>40700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-21600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-13100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>29700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-45900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-4300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -764,25 +764,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1677200</v>
+        <v>1709600</v>
       </c>
       <c r="E8" s="3">
-        <v>1389000</v>
+        <v>1415800</v>
       </c>
       <c r="F8" s="3">
-        <v>1241800</v>
+        <v>1265800</v>
       </c>
       <c r="G8" s="3">
-        <v>1104900</v>
+        <v>1126200</v>
       </c>
       <c r="H8" s="3">
-        <v>1172000</v>
+        <v>1194600</v>
       </c>
       <c r="I8" s="3">
-        <v>1075500</v>
+        <v>1096300</v>
       </c>
       <c r="J8" s="3">
-        <v>1152600</v>
+        <v>1174800</v>
       </c>
       <c r="K8" s="3">
         <v>750100</v>
@@ -829,25 +829,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1214000</v>
+        <v>1237400</v>
       </c>
       <c r="E9" s="3">
-        <v>1053800</v>
+        <v>1074100</v>
       </c>
       <c r="F9" s="3">
-        <v>1055400</v>
+        <v>1075800</v>
       </c>
       <c r="G9" s="3">
-        <v>986900</v>
+        <v>1006000</v>
       </c>
       <c r="H9" s="3">
-        <v>1013200</v>
+        <v>1032800</v>
       </c>
       <c r="I9" s="3">
-        <v>921600</v>
+        <v>939400</v>
       </c>
       <c r="J9" s="3">
-        <v>898600</v>
+        <v>915900</v>
       </c>
       <c r="K9" s="3">
         <v>675300</v>
@@ -894,25 +894,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>463300</v>
+        <v>472200</v>
       </c>
       <c r="E10" s="3">
-        <v>335200</v>
+        <v>341700</v>
       </c>
       <c r="F10" s="3">
-        <v>186400</v>
+        <v>190000</v>
       </c>
       <c r="G10" s="3">
-        <v>117900</v>
+        <v>120200</v>
       </c>
       <c r="H10" s="3">
-        <v>158700</v>
+        <v>161800</v>
       </c>
       <c r="I10" s="3">
-        <v>153900</v>
+        <v>156900</v>
       </c>
       <c r="J10" s="3">
-        <v>254000</v>
+        <v>258900</v>
       </c>
       <c r="K10" s="3">
         <v>74700</v>
@@ -984,22 +984,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>30600</v>
+        <v>31200</v>
       </c>
       <c r="E12" s="3">
-        <v>18600</v>
+        <v>18900</v>
       </c>
       <c r="F12" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="G12" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="H12" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="I12" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="J12" s="3">
         <v>4100</v>
@@ -1114,22 +1114,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="E14" s="3">
-        <v>-33700</v>
+        <v>-34300</v>
       </c>
       <c r="F14" s="3">
-        <v>36900</v>
+        <v>37700</v>
       </c>
       <c r="G14" s="3">
-        <v>224900</v>
+        <v>229300</v>
       </c>
       <c r="H14" s="3">
-        <v>14600</v>
+        <v>14900</v>
       </c>
       <c r="I14" s="3">
-        <v>120000</v>
+        <v>122300</v>
       </c>
       <c r="J14" s="3">
         <v>-2200</v>
@@ -1266,25 +1266,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1273100</v>
+        <v>1297700</v>
       </c>
       <c r="E17" s="3">
-        <v>1152300</v>
+        <v>1174500</v>
       </c>
       <c r="F17" s="3">
-        <v>1111200</v>
+        <v>1132600</v>
       </c>
       <c r="G17" s="3">
-        <v>1234300</v>
+        <v>1258100</v>
       </c>
       <c r="H17" s="3">
-        <v>1082800</v>
+        <v>1103700</v>
       </c>
       <c r="I17" s="3">
-        <v>1074300</v>
+        <v>1095000</v>
       </c>
       <c r="J17" s="3">
-        <v>849000</v>
+        <v>865300</v>
       </c>
       <c r="K17" s="3">
         <v>861100</v>
@@ -1331,25 +1331,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>404100</v>
+        <v>411900</v>
       </c>
       <c r="E18" s="3">
-        <v>236700</v>
+        <v>241200</v>
       </c>
       <c r="F18" s="3">
-        <v>130600</v>
+        <v>133200</v>
       </c>
       <c r="G18" s="3">
-        <v>-129500</v>
+        <v>-132000</v>
       </c>
       <c r="H18" s="3">
-        <v>89200</v>
+        <v>90900</v>
       </c>
       <c r="I18" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J18" s="3">
-        <v>303600</v>
+        <v>309500</v>
       </c>
       <c r="K18" s="3">
         <v>-111000</v>
@@ -1421,25 +1421,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="E20" s="3">
-        <v>-10000</v>
+        <v>-10200</v>
       </c>
       <c r="F20" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="G20" s="3">
-        <v>-8200</v>
+        <v>-8300</v>
       </c>
       <c r="H20" s="3">
         <v>2400</v>
       </c>
       <c r="I20" s="3">
-        <v>-12000</v>
+        <v>-12200</v>
       </c>
       <c r="J20" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="K20" s="3">
         <v>-2600</v>
@@ -1486,25 +1486,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>528400</v>
+        <v>538600</v>
       </c>
       <c r="E21" s="3">
-        <v>224300</v>
+        <v>228600</v>
       </c>
       <c r="F21" s="3">
-        <v>219400</v>
+        <v>223700</v>
       </c>
       <c r="G21" s="3">
-        <v>-134300</v>
+        <v>-136900</v>
       </c>
       <c r="H21" s="3">
-        <v>188200</v>
+        <v>191800</v>
       </c>
       <c r="I21" s="3">
         <v>2200</v>
       </c>
       <c r="J21" s="3">
-        <v>405800</v>
+        <v>413600</v>
       </c>
       <c r="K21" s="3">
         <v>-126800</v>
@@ -1560,16 +1560,16 @@
         <v>16</v>
       </c>
       <c r="G22" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="H22" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J22" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
@@ -1616,25 +1616,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>401300</v>
+        <v>409000</v>
       </c>
       <c r="E23" s="3">
-        <v>226600</v>
+        <v>231000</v>
       </c>
       <c r="F23" s="3">
-        <v>126100</v>
+        <v>128500</v>
       </c>
       <c r="G23" s="3">
-        <v>-143900</v>
+        <v>-146700</v>
       </c>
       <c r="H23" s="3">
-        <v>87500</v>
+        <v>89100</v>
       </c>
       <c r="I23" s="3">
-        <v>-10800</v>
+        <v>-11000</v>
       </c>
       <c r="J23" s="3">
-        <v>301900</v>
+        <v>307700</v>
       </c>
       <c r="K23" s="3">
         <v>-113500</v>
@@ -1681,25 +1681,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>83100</v>
+        <v>84700</v>
       </c>
       <c r="E24" s="3">
-        <v>65300</v>
+        <v>66600</v>
       </c>
       <c r="F24" s="3">
-        <v>26700</v>
+        <v>27200</v>
       </c>
       <c r="G24" s="3">
-        <v>-14900</v>
+        <v>-15200</v>
       </c>
       <c r="H24" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="I24" s="3">
-        <v>25900</v>
+        <v>26400</v>
       </c>
       <c r="J24" s="3">
-        <v>56300</v>
+        <v>57400</v>
       </c>
       <c r="K24" s="3">
         <v>5300</v>
@@ -1811,25 +1811,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>318200</v>
+        <v>324300</v>
       </c>
       <c r="E26" s="3">
-        <v>161300</v>
+        <v>164500</v>
       </c>
       <c r="F26" s="3">
-        <v>99400</v>
+        <v>101300</v>
       </c>
       <c r="G26" s="3">
-        <v>-129000</v>
+        <v>-131500</v>
       </c>
       <c r="H26" s="3">
-        <v>75000</v>
+        <v>76400</v>
       </c>
       <c r="I26" s="3">
-        <v>-36700</v>
+        <v>-37400</v>
       </c>
       <c r="J26" s="3">
-        <v>245600</v>
+        <v>250300</v>
       </c>
       <c r="K26" s="3">
         <v>-118900</v>
@@ -1876,25 +1876,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>316100</v>
+        <v>322200</v>
       </c>
       <c r="E27" s="3">
-        <v>159200</v>
+        <v>162200</v>
       </c>
       <c r="F27" s="3">
-        <v>98200</v>
+        <v>100100</v>
       </c>
       <c r="G27" s="3">
-        <v>-130200</v>
+        <v>-132700</v>
       </c>
       <c r="H27" s="3">
-        <v>74100</v>
+        <v>75500</v>
       </c>
       <c r="I27" s="3">
-        <v>-37300</v>
+        <v>-38000</v>
       </c>
       <c r="J27" s="3">
-        <v>244200</v>
+        <v>248900</v>
       </c>
       <c r="K27" s="3">
         <v>-120400</v>
@@ -2201,25 +2201,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E32" s="3">
-        <v>10000</v>
+        <v>10200</v>
       </c>
       <c r="F32" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G32" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="H32" s="3">
         <v>-2400</v>
       </c>
       <c r="I32" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="J32" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="K32" s="3">
         <v>2600</v>
@@ -2266,25 +2266,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>316100</v>
+        <v>322200</v>
       </c>
       <c r="E33" s="3">
-        <v>159200</v>
+        <v>162200</v>
       </c>
       <c r="F33" s="3">
-        <v>98200</v>
+        <v>100100</v>
       </c>
       <c r="G33" s="3">
-        <v>-130200</v>
+        <v>-132700</v>
       </c>
       <c r="H33" s="3">
-        <v>74100</v>
+        <v>75500</v>
       </c>
       <c r="I33" s="3">
-        <v>-37300</v>
+        <v>-38000</v>
       </c>
       <c r="J33" s="3">
-        <v>244200</v>
+        <v>248900</v>
       </c>
       <c r="K33" s="3">
         <v>-120400</v>
@@ -2396,25 +2396,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>316100</v>
+        <v>322200</v>
       </c>
       <c r="E35" s="3">
-        <v>159200</v>
+        <v>162200</v>
       </c>
       <c r="F35" s="3">
-        <v>98200</v>
+        <v>100100</v>
       </c>
       <c r="G35" s="3">
-        <v>-130200</v>
+        <v>-132700</v>
       </c>
       <c r="H35" s="3">
-        <v>74100</v>
+        <v>75500</v>
       </c>
       <c r="I35" s="3">
-        <v>-37300</v>
+        <v>-38000</v>
       </c>
       <c r="J35" s="3">
-        <v>244200</v>
+        <v>248900</v>
       </c>
       <c r="K35" s="3">
         <v>-120400</v>
@@ -2581,25 +2581,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>183400</v>
+        <v>187000</v>
       </c>
       <c r="E41" s="3">
-        <v>153100</v>
+        <v>156000</v>
       </c>
       <c r="F41" s="3">
-        <v>117200</v>
+        <v>119500</v>
       </c>
       <c r="G41" s="3">
-        <v>130700</v>
+        <v>133200</v>
       </c>
       <c r="H41" s="3">
-        <v>157000</v>
+        <v>160000</v>
       </c>
       <c r="I41" s="3">
-        <v>150500</v>
+        <v>153400</v>
       </c>
       <c r="J41" s="3">
-        <v>225100</v>
+        <v>229500</v>
       </c>
       <c r="K41" s="3">
         <v>346300</v>
@@ -2711,25 +2711,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>175500</v>
+        <v>178900</v>
       </c>
       <c r="E43" s="3">
-        <v>127900</v>
+        <v>130300</v>
       </c>
       <c r="F43" s="3">
-        <v>124200</v>
+        <v>126600</v>
       </c>
       <c r="G43" s="3">
-        <v>89800</v>
+        <v>91500</v>
       </c>
       <c r="H43" s="3">
-        <v>100600</v>
+        <v>102500</v>
       </c>
       <c r="I43" s="3">
-        <v>88200</v>
+        <v>89900</v>
       </c>
       <c r="J43" s="3">
-        <v>79300</v>
+        <v>80800</v>
       </c>
       <c r="K43" s="3">
         <v>71300</v>
@@ -2776,25 +2776,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>171500</v>
+        <v>174900</v>
       </c>
       <c r="E44" s="3">
-        <v>174300</v>
+        <v>177700</v>
       </c>
       <c r="F44" s="3">
-        <v>146500</v>
+        <v>149300</v>
       </c>
       <c r="G44" s="3">
-        <v>150500</v>
+        <v>153400</v>
       </c>
       <c r="H44" s="3">
-        <v>119100</v>
+        <v>121400</v>
       </c>
       <c r="I44" s="3">
-        <v>135700</v>
+        <v>138300</v>
       </c>
       <c r="J44" s="3">
-        <v>117400</v>
+        <v>119700</v>
       </c>
       <c r="K44" s="3">
         <v>131900</v>
@@ -2841,25 +2841,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15100</v>
+        <v>15300</v>
       </c>
       <c r="E45" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="F45" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="G45" s="3">
-        <v>29200</v>
+        <v>29700</v>
       </c>
       <c r="H45" s="3">
-        <v>35600</v>
+        <v>36200</v>
       </c>
       <c r="I45" s="3">
-        <v>82100</v>
+        <v>83700</v>
       </c>
       <c r="J45" s="3">
-        <v>42200</v>
+        <v>43000</v>
       </c>
       <c r="K45" s="3">
         <v>4400</v>
@@ -2906,25 +2906,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>545500</v>
+        <v>556100</v>
       </c>
       <c r="E46" s="3">
-        <v>463300</v>
+        <v>472300</v>
       </c>
       <c r="F46" s="3">
-        <v>407500</v>
+        <v>415300</v>
       </c>
       <c r="G46" s="3">
-        <v>400100</v>
+        <v>407800</v>
       </c>
       <c r="H46" s="3">
-        <v>412200</v>
+        <v>420100</v>
       </c>
       <c r="I46" s="3">
-        <v>456500</v>
+        <v>465300</v>
       </c>
       <c r="J46" s="3">
-        <v>464000</v>
+        <v>473000</v>
       </c>
       <c r="K46" s="3">
         <v>553800</v>
@@ -2971,25 +2971,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>23000</v>
+        <v>23500</v>
       </c>
       <c r="E47" s="3">
-        <v>23700</v>
+        <v>24100</v>
       </c>
       <c r="F47" s="3">
-        <v>23700</v>
+        <v>24100</v>
       </c>
       <c r="G47" s="3">
-        <v>26600</v>
+        <v>27200</v>
       </c>
       <c r="H47" s="3">
-        <v>23800</v>
+        <v>24200</v>
       </c>
       <c r="I47" s="3">
-        <v>24500</v>
+        <v>24900</v>
       </c>
       <c r="J47" s="3">
-        <v>30900</v>
+        <v>31500</v>
       </c>
       <c r="K47" s="3">
         <v>29100</v>
@@ -3036,25 +3036,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2269400</v>
+        <v>2313200</v>
       </c>
       <c r="E48" s="3">
-        <v>2216100</v>
+        <v>2258800</v>
       </c>
       <c r="F48" s="3">
-        <v>2045300</v>
+        <v>2084700</v>
       </c>
       <c r="G48" s="3">
-        <v>1755000</v>
+        <v>1788900</v>
       </c>
       <c r="H48" s="3">
-        <v>1909200</v>
+        <v>1946100</v>
       </c>
       <c r="I48" s="3">
-        <v>1793700</v>
+        <v>1828300</v>
       </c>
       <c r="J48" s="3">
-        <v>1847200</v>
+        <v>1882800</v>
       </c>
       <c r="K48" s="3">
         <v>1590100</v>
@@ -3107,19 +3107,19 @@
         <v>1800</v>
       </c>
       <c r="F49" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G49" s="3">
         <v>2600</v>
       </c>
       <c r="H49" s="3">
-        <v>18600</v>
+        <v>19000</v>
       </c>
       <c r="I49" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="J49" s="3">
-        <v>28900</v>
+        <v>29500</v>
       </c>
       <c r="K49" s="3">
         <v>29200</v>
@@ -3296,25 +3296,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>352600</v>
+        <v>359400</v>
       </c>
       <c r="E52" s="3">
-        <v>351300</v>
+        <v>358000</v>
       </c>
       <c r="F52" s="3">
-        <v>336200</v>
+        <v>342700</v>
       </c>
       <c r="G52" s="3">
-        <v>314700</v>
+        <v>320800</v>
       </c>
       <c r="H52" s="3">
-        <v>307600</v>
+        <v>313500</v>
       </c>
       <c r="I52" s="3">
-        <v>311400</v>
+        <v>317400</v>
       </c>
       <c r="J52" s="3">
-        <v>339100</v>
+        <v>345600</v>
       </c>
       <c r="K52" s="3">
         <v>232600</v>
@@ -3426,25 +3426,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3192000</v>
+        <v>3253600</v>
       </c>
       <c r="E54" s="3">
-        <v>3056000</v>
+        <v>3115000</v>
       </c>
       <c r="F54" s="3">
-        <v>2814700</v>
+        <v>2869000</v>
       </c>
       <c r="G54" s="3">
-        <v>2499100</v>
+        <v>2547300</v>
       </c>
       <c r="H54" s="3">
-        <v>2671400</v>
+        <v>2722900</v>
       </c>
       <c r="I54" s="3">
-        <v>2605600</v>
+        <v>2655900</v>
       </c>
       <c r="J54" s="3">
-        <v>2700300</v>
+        <v>2752300</v>
       </c>
       <c r="K54" s="3">
         <v>2434800</v>
@@ -3541,25 +3541,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>275500</v>
+        <v>280900</v>
       </c>
       <c r="E57" s="3">
-        <v>279700</v>
+        <v>285100</v>
       </c>
       <c r="F57" s="3">
-        <v>244900</v>
+        <v>249600</v>
       </c>
       <c r="G57" s="3">
-        <v>239900</v>
+        <v>244600</v>
       </c>
       <c r="H57" s="3">
-        <v>224100</v>
+        <v>228400</v>
       </c>
       <c r="I57" s="3">
-        <v>234300</v>
+        <v>238800</v>
       </c>
       <c r="J57" s="3">
-        <v>209500</v>
+        <v>213500</v>
       </c>
       <c r="K57" s="3">
         <v>163800</v>
@@ -3606,25 +3606,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H58" s="3">
-        <v>20000</v>
+        <v>20400</v>
       </c>
       <c r="I58" s="3">
-        <v>20700</v>
+        <v>21100</v>
       </c>
       <c r="J58" s="3">
-        <v>20800</v>
+        <v>21200</v>
       </c>
       <c r="K58" s="3">
         <v>13900</v>
@@ -3671,25 +3671,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>61500</v>
+        <v>62600</v>
       </c>
       <c r="E59" s="3">
-        <v>81500</v>
+        <v>83000</v>
       </c>
       <c r="F59" s="3">
-        <v>24000</v>
+        <v>24400</v>
       </c>
       <c r="G59" s="3">
-        <v>24300</v>
+        <v>24800</v>
       </c>
       <c r="H59" s="3">
-        <v>31700</v>
+        <v>32300</v>
       </c>
       <c r="I59" s="3">
-        <v>41500</v>
+        <v>42300</v>
       </c>
       <c r="J59" s="3">
-        <v>117000</v>
+        <v>119300</v>
       </c>
       <c r="K59" s="3">
         <v>234200</v>
@@ -3736,25 +3736,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>337700</v>
+        <v>344300</v>
       </c>
       <c r="E60" s="3">
-        <v>366600</v>
+        <v>373700</v>
       </c>
       <c r="F60" s="3">
-        <v>268900</v>
+        <v>274100</v>
       </c>
       <c r="G60" s="3">
-        <v>265600</v>
+        <v>270700</v>
       </c>
       <c r="H60" s="3">
-        <v>275700</v>
+        <v>281000</v>
       </c>
       <c r="I60" s="3">
-        <v>296500</v>
+        <v>302200</v>
       </c>
       <c r="J60" s="3">
-        <v>347400</v>
+        <v>354100</v>
       </c>
       <c r="K60" s="3">
         <v>411900</v>
@@ -3801,25 +3801,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>178700</v>
+        <v>182200</v>
       </c>
       <c r="E61" s="3">
-        <v>298600</v>
+        <v>304300</v>
       </c>
       <c r="F61" s="3">
-        <v>368700</v>
+        <v>375800</v>
       </c>
       <c r="G61" s="3">
-        <v>169800</v>
+        <v>173100</v>
       </c>
       <c r="H61" s="3">
-        <v>169700</v>
+        <v>172900</v>
       </c>
       <c r="I61" s="3">
-        <v>158800</v>
+        <v>161800</v>
       </c>
       <c r="J61" s="3">
-        <v>235300</v>
+        <v>239800</v>
       </c>
       <c r="K61" s="3">
         <v>406600</v>
@@ -3866,25 +3866,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>541200</v>
+        <v>551700</v>
       </c>
       <c r="E62" s="3">
-        <v>528600</v>
+        <v>538800</v>
       </c>
       <c r="F62" s="3">
-        <v>479900</v>
+        <v>489100</v>
       </c>
       <c r="G62" s="3">
-        <v>455700</v>
+        <v>464500</v>
       </c>
       <c r="H62" s="3">
-        <v>488000</v>
+        <v>497400</v>
       </c>
       <c r="I62" s="3">
-        <v>483800</v>
+        <v>493200</v>
       </c>
       <c r="J62" s="3">
-        <v>574200</v>
+        <v>585300</v>
       </c>
       <c r="K62" s="3">
         <v>342900</v>
@@ -4126,25 +4126,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1065300</v>
+        <v>1085800</v>
       </c>
       <c r="E66" s="3">
-        <v>1200400</v>
+        <v>1223500</v>
       </c>
       <c r="F66" s="3">
-        <v>1122200</v>
+        <v>1143900</v>
       </c>
       <c r="G66" s="3">
-        <v>895300</v>
+        <v>912600</v>
       </c>
       <c r="H66" s="3">
-        <v>936800</v>
+        <v>954900</v>
       </c>
       <c r="I66" s="3">
-        <v>942000</v>
+        <v>960100</v>
       </c>
       <c r="J66" s="3">
-        <v>1111700</v>
+        <v>1133200</v>
       </c>
       <c r="K66" s="3">
         <v>1161600</v>
@@ -4476,25 +4476,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>368300</v>
+        <v>375400</v>
       </c>
       <c r="E72" s="3">
-        <v>97300</v>
+        <v>99200</v>
       </c>
       <c r="F72" s="3">
-        <v>-65800</v>
+        <v>-67100</v>
       </c>
       <c r="G72" s="3">
-        <v>-154600</v>
+        <v>-157500</v>
       </c>
       <c r="H72" s="3">
-        <v>-23800</v>
+        <v>-24200</v>
       </c>
       <c r="I72" s="3">
-        <v>-94700</v>
+        <v>-96500</v>
       </c>
       <c r="J72" s="3">
-        <v>-169900</v>
+        <v>-173200</v>
       </c>
       <c r="K72" s="3">
         <v>-521200</v>
@@ -4736,25 +4736,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2126700</v>
+        <v>2167700</v>
       </c>
       <c r="E76" s="3">
-        <v>1855700</v>
+        <v>1891500</v>
       </c>
       <c r="F76" s="3">
-        <v>1692500</v>
+        <v>1725200</v>
       </c>
       <c r="G76" s="3">
-        <v>1603800</v>
+        <v>1634700</v>
       </c>
       <c r="H76" s="3">
-        <v>1734600</v>
+        <v>1768100</v>
       </c>
       <c r="I76" s="3">
-        <v>1663600</v>
+        <v>1695700</v>
       </c>
       <c r="J76" s="3">
-        <v>1588500</v>
+        <v>1619200</v>
       </c>
       <c r="K76" s="3">
         <v>1273300</v>
@@ -4936,25 +4936,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>316100</v>
+        <v>322200</v>
       </c>
       <c r="E81" s="3">
-        <v>159200</v>
+        <v>162200</v>
       </c>
       <c r="F81" s="3">
-        <v>98200</v>
+        <v>100100</v>
       </c>
       <c r="G81" s="3">
-        <v>-130200</v>
+        <v>-132700</v>
       </c>
       <c r="H81" s="3">
-        <v>74100</v>
+        <v>75500</v>
       </c>
       <c r="I81" s="3">
-        <v>-37300</v>
+        <v>-38000</v>
       </c>
       <c r="J81" s="3">
-        <v>244200</v>
+        <v>248900</v>
       </c>
       <c r="K81" s="3">
         <v>-120400</v>
@@ -5416,25 +5416,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>373500</v>
+        <v>380700</v>
       </c>
       <c r="E89" s="3">
-        <v>367500</v>
+        <v>374600</v>
       </c>
       <c r="F89" s="3">
-        <v>163600</v>
+        <v>166800</v>
       </c>
       <c r="G89" s="3">
-        <v>-1428600</v>
+        <v>-1456100</v>
       </c>
       <c r="H89" s="3">
-        <v>1798200</v>
+        <v>1832900</v>
       </c>
       <c r="I89" s="3">
-        <v>181500</v>
+        <v>185000</v>
       </c>
       <c r="J89" s="3">
-        <v>308500</v>
+        <v>314500</v>
       </c>
       <c r="K89" s="3">
         <v>108400</v>
@@ -5701,25 +5701,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-199000</v>
+        <v>-202900</v>
       </c>
       <c r="E94" s="3">
-        <v>-209100</v>
+        <v>-213200</v>
       </c>
       <c r="F94" s="3">
-        <v>-356600</v>
+        <v>-363500</v>
       </c>
       <c r="G94" s="3">
-        <v>1437300</v>
+        <v>1465000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1768300</v>
+        <v>-1802400</v>
       </c>
       <c r="I94" s="3">
-        <v>-149200</v>
+        <v>-152000</v>
       </c>
       <c r="J94" s="3">
-        <v>-302700</v>
+        <v>-308600</v>
       </c>
       <c r="K94" s="3">
         <v>-72700</v>
@@ -5791,19 +5791,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-25900</v>
+        <v>-26400</v>
       </c>
       <c r="E96" s="3">
         <v>-500</v>
       </c>
       <c r="F96" s="3">
-        <v>-7700</v>
+        <v>-7900</v>
       </c>
       <c r="G96" s="3">
-        <v>-13700</v>
+        <v>-14000</v>
       </c>
       <c r="H96" s="3">
-        <v>-9200</v>
+        <v>-9400</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -6051,25 +6051,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-146500</v>
+        <v>-149300</v>
       </c>
       <c r="E100" s="3">
-        <v>-113800</v>
+        <v>-116000</v>
       </c>
       <c r="F100" s="3">
-        <v>177500</v>
+        <v>180900</v>
       </c>
       <c r="G100" s="3">
-        <v>-37900</v>
+        <v>-38600</v>
       </c>
       <c r="H100" s="3">
-        <v>-23600</v>
+        <v>-24100</v>
       </c>
       <c r="I100" s="3">
-        <v>-114000</v>
+        <v>-116200</v>
       </c>
       <c r="J100" s="3">
-        <v>-115500</v>
+        <v>-117800</v>
       </c>
       <c r="K100" s="3">
         <v>250100</v>
@@ -6119,10 +6119,10 @@
         <v>2500</v>
       </c>
       <c r="E101" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="F101" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G101" s="3">
         <v>2900</v>
@@ -6131,10 +6131,10 @@
         <v>100</v>
       </c>
       <c r="I101" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="J101" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="K101" s="3">
         <v>-7500</v>
@@ -6181,25 +6181,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>30400</v>
+        <v>31000</v>
       </c>
       <c r="E102" s="3">
-        <v>35900</v>
+        <v>36600</v>
       </c>
       <c r="F102" s="3">
-        <v>-13500</v>
+        <v>-13800</v>
       </c>
       <c r="G102" s="3">
-        <v>-26300</v>
+        <v>-26800</v>
       </c>
       <c r="H102" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="I102" s="3">
-        <v>-74600</v>
+        <v>-76100</v>
       </c>
       <c r="J102" s="3">
-        <v>-114300</v>
+        <v>-116500</v>
       </c>
       <c r="K102" s="3">
         <v>278200</v>

--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -764,25 +764,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1709600</v>
+        <v>1770200</v>
       </c>
       <c r="E8" s="3">
-        <v>1415800</v>
+        <v>1466000</v>
       </c>
       <c r="F8" s="3">
-        <v>1265800</v>
+        <v>1310600</v>
       </c>
       <c r="G8" s="3">
-        <v>1126200</v>
+        <v>1166100</v>
       </c>
       <c r="H8" s="3">
-        <v>1194600</v>
+        <v>1236900</v>
       </c>
       <c r="I8" s="3">
-        <v>1096300</v>
+        <v>1135200</v>
       </c>
       <c r="J8" s="3">
-        <v>1174800</v>
+        <v>1216500</v>
       </c>
       <c r="K8" s="3">
         <v>750100</v>
@@ -829,25 +829,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1237400</v>
+        <v>1281300</v>
       </c>
       <c r="E9" s="3">
-        <v>1074100</v>
+        <v>1112200</v>
       </c>
       <c r="F9" s="3">
-        <v>1075800</v>
+        <v>1113900</v>
       </c>
       <c r="G9" s="3">
-        <v>1006000</v>
+        <v>1041600</v>
       </c>
       <c r="H9" s="3">
-        <v>1032800</v>
+        <v>1069400</v>
       </c>
       <c r="I9" s="3">
-        <v>939400</v>
+        <v>972700</v>
       </c>
       <c r="J9" s="3">
-        <v>915900</v>
+        <v>948400</v>
       </c>
       <c r="K9" s="3">
         <v>675300</v>
@@ -894,25 +894,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>472200</v>
+        <v>488900</v>
       </c>
       <c r="E10" s="3">
-        <v>341700</v>
+        <v>353800</v>
       </c>
       <c r="F10" s="3">
-        <v>190000</v>
+        <v>196700</v>
       </c>
       <c r="G10" s="3">
-        <v>120200</v>
+        <v>124500</v>
       </c>
       <c r="H10" s="3">
-        <v>161800</v>
+        <v>167500</v>
       </c>
       <c r="I10" s="3">
-        <v>156900</v>
+        <v>162500</v>
       </c>
       <c r="J10" s="3">
-        <v>258900</v>
+        <v>268100</v>
       </c>
       <c r="K10" s="3">
         <v>74700</v>
@@ -984,25 +984,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>31200</v>
+        <v>32300</v>
       </c>
       <c r="E12" s="3">
-        <v>18900</v>
+        <v>19600</v>
       </c>
       <c r="F12" s="3">
-        <v>8600</v>
+        <v>8900</v>
       </c>
       <c r="G12" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="H12" s="3">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="I12" s="3">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="J12" s="3">
-        <v>4100</v>
+        <v>4300</v>
       </c>
       <c r="K12" s="3">
         <v>4200</v>
@@ -1114,25 +1114,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E14" s="3">
-        <v>-34300</v>
+        <v>-35600</v>
       </c>
       <c r="F14" s="3">
-        <v>37700</v>
+        <v>39000</v>
       </c>
       <c r="G14" s="3">
-        <v>229300</v>
+        <v>237400</v>
       </c>
       <c r="H14" s="3">
-        <v>14900</v>
+        <v>15400</v>
       </c>
       <c r="I14" s="3">
-        <v>122300</v>
+        <v>126700</v>
       </c>
       <c r="J14" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K14" s="3">
         <v>5200</v>
@@ -1266,25 +1266,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1297700</v>
+        <v>1343700</v>
       </c>
       <c r="E17" s="3">
-        <v>1174500</v>
+        <v>1216200</v>
       </c>
       <c r="F17" s="3">
-        <v>1132600</v>
+        <v>1172800</v>
       </c>
       <c r="G17" s="3">
-        <v>1258100</v>
+        <v>1302800</v>
       </c>
       <c r="H17" s="3">
-        <v>1103700</v>
+        <v>1142800</v>
       </c>
       <c r="I17" s="3">
-        <v>1095000</v>
+        <v>1133900</v>
       </c>
       <c r="J17" s="3">
-        <v>865300</v>
+        <v>896000</v>
       </c>
       <c r="K17" s="3">
         <v>861100</v>
@@ -1331,25 +1331,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>411900</v>
+        <v>426500</v>
       </c>
       <c r="E18" s="3">
-        <v>241200</v>
+        <v>249800</v>
       </c>
       <c r="F18" s="3">
-        <v>133200</v>
+        <v>137900</v>
       </c>
       <c r="G18" s="3">
-        <v>-132000</v>
+        <v>-136600</v>
       </c>
       <c r="H18" s="3">
-        <v>90900</v>
+        <v>94100</v>
       </c>
       <c r="I18" s="3">
         <v>1300</v>
       </c>
       <c r="J18" s="3">
-        <v>309500</v>
+        <v>320500</v>
       </c>
       <c r="K18" s="3">
         <v>-111000</v>
@@ -1421,25 +1421,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
-        <v>-10200</v>
+        <v>-10600</v>
       </c>
       <c r="F20" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="G20" s="3">
-        <v>-8300</v>
+        <v>-8600</v>
       </c>
       <c r="H20" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="I20" s="3">
-        <v>-12200</v>
+        <v>-12700</v>
       </c>
       <c r="J20" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="K20" s="3">
         <v>-2600</v>
@@ -1486,25 +1486,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>538600</v>
+        <v>557700</v>
       </c>
       <c r="E21" s="3">
-        <v>228600</v>
+        <v>236700</v>
       </c>
       <c r="F21" s="3">
-        <v>223700</v>
+        <v>231600</v>
       </c>
       <c r="G21" s="3">
-        <v>-136900</v>
+        <v>-141700</v>
       </c>
       <c r="H21" s="3">
-        <v>191800</v>
+        <v>198600</v>
       </c>
       <c r="I21" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J21" s="3">
-        <v>413600</v>
+        <v>428300</v>
       </c>
       <c r="K21" s="3">
         <v>-126800</v>
@@ -1560,16 +1560,16 @@
         <v>16</v>
       </c>
       <c r="G22" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="H22" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J22" s="3">
-        <v>7100</v>
+        <v>7300</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
@@ -1616,25 +1616,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>409000</v>
+        <v>423500</v>
       </c>
       <c r="E23" s="3">
-        <v>231000</v>
+        <v>239200</v>
       </c>
       <c r="F23" s="3">
-        <v>128500</v>
+        <v>133000</v>
       </c>
       <c r="G23" s="3">
-        <v>-146700</v>
+        <v>-151900</v>
       </c>
       <c r="H23" s="3">
-        <v>89100</v>
+        <v>92300</v>
       </c>
       <c r="I23" s="3">
-        <v>-11000</v>
+        <v>-11400</v>
       </c>
       <c r="J23" s="3">
-        <v>307700</v>
+        <v>318600</v>
       </c>
       <c r="K23" s="3">
         <v>-113500</v>
@@ -1681,25 +1681,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>84700</v>
+        <v>87700</v>
       </c>
       <c r="E24" s="3">
-        <v>66600</v>
+        <v>68900</v>
       </c>
       <c r="F24" s="3">
-        <v>27200</v>
+        <v>28200</v>
       </c>
       <c r="G24" s="3">
-        <v>-15200</v>
+        <v>-15800</v>
       </c>
       <c r="H24" s="3">
-        <v>12700</v>
+        <v>13200</v>
       </c>
       <c r="I24" s="3">
-        <v>26400</v>
+        <v>27400</v>
       </c>
       <c r="J24" s="3">
-        <v>57400</v>
+        <v>59400</v>
       </c>
       <c r="K24" s="3">
         <v>5300</v>
@@ -1811,25 +1811,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>324300</v>
+        <v>335800</v>
       </c>
       <c r="E26" s="3">
-        <v>164500</v>
+        <v>170300</v>
       </c>
       <c r="F26" s="3">
-        <v>101300</v>
+        <v>104900</v>
       </c>
       <c r="G26" s="3">
-        <v>-131500</v>
+        <v>-136100</v>
       </c>
       <c r="H26" s="3">
-        <v>76400</v>
+        <v>79100</v>
       </c>
       <c r="I26" s="3">
-        <v>-37400</v>
+        <v>-38800</v>
       </c>
       <c r="J26" s="3">
-        <v>250300</v>
+        <v>259200</v>
       </c>
       <c r="K26" s="3">
         <v>-118900</v>
@@ -1876,25 +1876,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>322200</v>
+        <v>333600</v>
       </c>
       <c r="E27" s="3">
-        <v>162200</v>
+        <v>168000</v>
       </c>
       <c r="F27" s="3">
-        <v>100100</v>
+        <v>103600</v>
       </c>
       <c r="G27" s="3">
-        <v>-132700</v>
+        <v>-137400</v>
       </c>
       <c r="H27" s="3">
-        <v>75500</v>
+        <v>78200</v>
       </c>
       <c r="I27" s="3">
-        <v>-38000</v>
+        <v>-39300</v>
       </c>
       <c r="J27" s="3">
-        <v>248900</v>
+        <v>257700</v>
       </c>
       <c r="K27" s="3">
         <v>-120400</v>
@@ -2201,25 +2201,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
-        <v>10200</v>
+        <v>10600</v>
       </c>
       <c r="F32" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="G32" s="3">
-        <v>8300</v>
+        <v>8600</v>
       </c>
       <c r="H32" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="I32" s="3">
-        <v>12200</v>
+        <v>12700</v>
       </c>
       <c r="J32" s="3">
-        <v>-5300</v>
+        <v>-5500</v>
       </c>
       <c r="K32" s="3">
         <v>2600</v>
@@ -2266,25 +2266,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>322200</v>
+        <v>333600</v>
       </c>
       <c r="E33" s="3">
-        <v>162200</v>
+        <v>168000</v>
       </c>
       <c r="F33" s="3">
-        <v>100100</v>
+        <v>103600</v>
       </c>
       <c r="G33" s="3">
-        <v>-132700</v>
+        <v>-137400</v>
       </c>
       <c r="H33" s="3">
-        <v>75500</v>
+        <v>78200</v>
       </c>
       <c r="I33" s="3">
-        <v>-38000</v>
+        <v>-39300</v>
       </c>
       <c r="J33" s="3">
-        <v>248900</v>
+        <v>257700</v>
       </c>
       <c r="K33" s="3">
         <v>-120400</v>
@@ -2396,25 +2396,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>322200</v>
+        <v>333600</v>
       </c>
       <c r="E35" s="3">
-        <v>162200</v>
+        <v>168000</v>
       </c>
       <c r="F35" s="3">
-        <v>100100</v>
+        <v>103600</v>
       </c>
       <c r="G35" s="3">
-        <v>-132700</v>
+        <v>-137400</v>
       </c>
       <c r="H35" s="3">
-        <v>75500</v>
+        <v>78200</v>
       </c>
       <c r="I35" s="3">
-        <v>-38000</v>
+        <v>-39300</v>
       </c>
       <c r="J35" s="3">
-        <v>248900</v>
+        <v>257700</v>
       </c>
       <c r="K35" s="3">
         <v>-120400</v>
@@ -2581,25 +2581,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>187000</v>
+        <v>193600</v>
       </c>
       <c r="E41" s="3">
-        <v>156000</v>
+        <v>161600</v>
       </c>
       <c r="F41" s="3">
-        <v>119500</v>
+        <v>123700</v>
       </c>
       <c r="G41" s="3">
-        <v>133200</v>
+        <v>137900</v>
       </c>
       <c r="H41" s="3">
-        <v>160000</v>
+        <v>165700</v>
       </c>
       <c r="I41" s="3">
-        <v>153400</v>
+        <v>158900</v>
       </c>
       <c r="J41" s="3">
-        <v>229500</v>
+        <v>237600</v>
       </c>
       <c r="K41" s="3">
         <v>346300</v>
@@ -2711,25 +2711,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>178900</v>
+        <v>185200</v>
       </c>
       <c r="E43" s="3">
-        <v>130300</v>
+        <v>135000</v>
       </c>
       <c r="F43" s="3">
-        <v>126600</v>
+        <v>131100</v>
       </c>
       <c r="G43" s="3">
-        <v>91500</v>
+        <v>94800</v>
       </c>
       <c r="H43" s="3">
-        <v>102500</v>
+        <v>106200</v>
       </c>
       <c r="I43" s="3">
-        <v>89900</v>
+        <v>93100</v>
       </c>
       <c r="J43" s="3">
-        <v>80800</v>
+        <v>83700</v>
       </c>
       <c r="K43" s="3">
         <v>71300</v>
@@ -2776,25 +2776,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>174900</v>
+        <v>181100</v>
       </c>
       <c r="E44" s="3">
-        <v>177700</v>
+        <v>184000</v>
       </c>
       <c r="F44" s="3">
-        <v>149300</v>
+        <v>154600</v>
       </c>
       <c r="G44" s="3">
-        <v>153400</v>
+        <v>158800</v>
       </c>
       <c r="H44" s="3">
-        <v>121400</v>
+        <v>125700</v>
       </c>
       <c r="I44" s="3">
-        <v>138300</v>
+        <v>143200</v>
       </c>
       <c r="J44" s="3">
-        <v>119700</v>
+        <v>123900</v>
       </c>
       <c r="K44" s="3">
         <v>131900</v>
@@ -2841,25 +2841,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15300</v>
+        <v>15900</v>
       </c>
       <c r="E45" s="3">
-        <v>8200</v>
+        <v>8500</v>
       </c>
       <c r="F45" s="3">
-        <v>19900</v>
+        <v>20600</v>
       </c>
       <c r="G45" s="3">
-        <v>29700</v>
+        <v>30800</v>
       </c>
       <c r="H45" s="3">
-        <v>36200</v>
+        <v>37500</v>
       </c>
       <c r="I45" s="3">
-        <v>83700</v>
+        <v>86700</v>
       </c>
       <c r="J45" s="3">
-        <v>43000</v>
+        <v>44500</v>
       </c>
       <c r="K45" s="3">
         <v>4400</v>
@@ -2906,25 +2906,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>556100</v>
+        <v>575800</v>
       </c>
       <c r="E46" s="3">
-        <v>472300</v>
+        <v>489000</v>
       </c>
       <c r="F46" s="3">
-        <v>415300</v>
+        <v>430100</v>
       </c>
       <c r="G46" s="3">
-        <v>407800</v>
+        <v>422300</v>
       </c>
       <c r="H46" s="3">
-        <v>420100</v>
+        <v>435000</v>
       </c>
       <c r="I46" s="3">
-        <v>465300</v>
+        <v>481800</v>
       </c>
       <c r="J46" s="3">
-        <v>473000</v>
+        <v>489700</v>
       </c>
       <c r="K46" s="3">
         <v>553800</v>
@@ -2971,25 +2971,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>23500</v>
+        <v>24300</v>
       </c>
       <c r="E47" s="3">
-        <v>24100</v>
+        <v>25000</v>
       </c>
       <c r="F47" s="3">
-        <v>24100</v>
+        <v>25000</v>
       </c>
       <c r="G47" s="3">
-        <v>27200</v>
+        <v>28100</v>
       </c>
       <c r="H47" s="3">
-        <v>24200</v>
+        <v>25100</v>
       </c>
       <c r="I47" s="3">
-        <v>24900</v>
+        <v>25800</v>
       </c>
       <c r="J47" s="3">
-        <v>31500</v>
+        <v>32600</v>
       </c>
       <c r="K47" s="3">
         <v>29100</v>
@@ -3036,25 +3036,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2313200</v>
+        <v>2395200</v>
       </c>
       <c r="E48" s="3">
-        <v>2258800</v>
+        <v>2338900</v>
       </c>
       <c r="F48" s="3">
-        <v>2084700</v>
+        <v>2158700</v>
       </c>
       <c r="G48" s="3">
-        <v>1788900</v>
+        <v>1852300</v>
       </c>
       <c r="H48" s="3">
-        <v>1946100</v>
+        <v>2015100</v>
       </c>
       <c r="I48" s="3">
-        <v>1828300</v>
+        <v>1893200</v>
       </c>
       <c r="J48" s="3">
-        <v>1882800</v>
+        <v>1949600</v>
       </c>
       <c r="K48" s="3">
         <v>1590100</v>
@@ -3101,25 +3101,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E49" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="F49" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="G49" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="H49" s="3">
-        <v>19000</v>
+        <v>19700</v>
       </c>
       <c r="I49" s="3">
-        <v>19900</v>
+        <v>20600</v>
       </c>
       <c r="J49" s="3">
-        <v>29500</v>
+        <v>30500</v>
       </c>
       <c r="K49" s="3">
         <v>29200</v>
@@ -3296,25 +3296,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>359400</v>
+        <v>372200</v>
       </c>
       <c r="E52" s="3">
-        <v>358000</v>
+        <v>370700</v>
       </c>
       <c r="F52" s="3">
-        <v>342700</v>
+        <v>354800</v>
       </c>
       <c r="G52" s="3">
-        <v>320800</v>
+        <v>332200</v>
       </c>
       <c r="H52" s="3">
-        <v>313500</v>
+        <v>324600</v>
       </c>
       <c r="I52" s="3">
-        <v>317400</v>
+        <v>328600</v>
       </c>
       <c r="J52" s="3">
-        <v>345600</v>
+        <v>357900</v>
       </c>
       <c r="K52" s="3">
         <v>232600</v>
@@ -3426,25 +3426,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3253600</v>
+        <v>3368900</v>
       </c>
       <c r="E54" s="3">
-        <v>3115000</v>
+        <v>3225500</v>
       </c>
       <c r="F54" s="3">
-        <v>2869000</v>
+        <v>2970800</v>
       </c>
       <c r="G54" s="3">
-        <v>2547300</v>
+        <v>2637600</v>
       </c>
       <c r="H54" s="3">
-        <v>2722900</v>
+        <v>2819500</v>
       </c>
       <c r="I54" s="3">
-        <v>2655900</v>
+        <v>2750000</v>
       </c>
       <c r="J54" s="3">
-        <v>2752300</v>
+        <v>2850000</v>
       </c>
       <c r="K54" s="3">
         <v>2434800</v>
@@ -3541,25 +3541,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>280900</v>
+        <v>290800</v>
       </c>
       <c r="E57" s="3">
-        <v>285100</v>
+        <v>295200</v>
       </c>
       <c r="F57" s="3">
-        <v>249600</v>
+        <v>258500</v>
       </c>
       <c r="G57" s="3">
-        <v>244600</v>
+        <v>253200</v>
       </c>
       <c r="H57" s="3">
-        <v>228400</v>
+        <v>236500</v>
       </c>
       <c r="I57" s="3">
-        <v>238800</v>
+        <v>247300</v>
       </c>
       <c r="J57" s="3">
-        <v>213500</v>
+        <v>221100</v>
       </c>
       <c r="K57" s="3">
         <v>163800</v>
@@ -3609,7 +3609,7 @@
         <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3618,13 +3618,13 @@
         <v>1400</v>
       </c>
       <c r="H58" s="3">
-        <v>20400</v>
+        <v>21100</v>
       </c>
       <c r="I58" s="3">
-        <v>21100</v>
+        <v>21800</v>
       </c>
       <c r="J58" s="3">
-        <v>21200</v>
+        <v>22000</v>
       </c>
       <c r="K58" s="3">
         <v>13900</v>
@@ -3671,25 +3671,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>62600</v>
+        <v>64900</v>
       </c>
       <c r="E59" s="3">
-        <v>83000</v>
+        <v>86000</v>
       </c>
       <c r="F59" s="3">
-        <v>24400</v>
+        <v>25300</v>
       </c>
       <c r="G59" s="3">
-        <v>24800</v>
+        <v>25700</v>
       </c>
       <c r="H59" s="3">
-        <v>32300</v>
+        <v>33400</v>
       </c>
       <c r="I59" s="3">
-        <v>42300</v>
+        <v>43800</v>
       </c>
       <c r="J59" s="3">
-        <v>119300</v>
+        <v>123500</v>
       </c>
       <c r="K59" s="3">
         <v>234200</v>
@@ -3736,25 +3736,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>344300</v>
+        <v>356500</v>
       </c>
       <c r="E60" s="3">
-        <v>373700</v>
+        <v>387000</v>
       </c>
       <c r="F60" s="3">
-        <v>274100</v>
+        <v>283800</v>
       </c>
       <c r="G60" s="3">
-        <v>270700</v>
+        <v>280300</v>
       </c>
       <c r="H60" s="3">
-        <v>281000</v>
+        <v>291000</v>
       </c>
       <c r="I60" s="3">
-        <v>302200</v>
+        <v>312900</v>
       </c>
       <c r="J60" s="3">
-        <v>354100</v>
+        <v>366600</v>
       </c>
       <c r="K60" s="3">
         <v>411900</v>
@@ -3801,25 +3801,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>182200</v>
+        <v>188700</v>
       </c>
       <c r="E61" s="3">
-        <v>304300</v>
+        <v>315100</v>
       </c>
       <c r="F61" s="3">
-        <v>375800</v>
+        <v>389100</v>
       </c>
       <c r="G61" s="3">
-        <v>173100</v>
+        <v>179200</v>
       </c>
       <c r="H61" s="3">
-        <v>172900</v>
+        <v>179100</v>
       </c>
       <c r="I61" s="3">
-        <v>161800</v>
+        <v>167600</v>
       </c>
       <c r="J61" s="3">
-        <v>239800</v>
+        <v>248300</v>
       </c>
       <c r="K61" s="3">
         <v>406600</v>
@@ -3866,25 +3866,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>551700</v>
+        <v>571200</v>
       </c>
       <c r="E62" s="3">
-        <v>538800</v>
+        <v>557900</v>
       </c>
       <c r="F62" s="3">
-        <v>489100</v>
+        <v>506500</v>
       </c>
       <c r="G62" s="3">
-        <v>464500</v>
+        <v>481000</v>
       </c>
       <c r="H62" s="3">
-        <v>497400</v>
+        <v>515000</v>
       </c>
       <c r="I62" s="3">
-        <v>493200</v>
+        <v>510600</v>
       </c>
       <c r="J62" s="3">
-        <v>585300</v>
+        <v>606000</v>
       </c>
       <c r="K62" s="3">
         <v>342900</v>
@@ -4126,25 +4126,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1085800</v>
+        <v>1124400</v>
       </c>
       <c r="E66" s="3">
-        <v>1223500</v>
+        <v>1266900</v>
       </c>
       <c r="F66" s="3">
-        <v>1143900</v>
+        <v>1184400</v>
       </c>
       <c r="G66" s="3">
-        <v>912600</v>
+        <v>944900</v>
       </c>
       <c r="H66" s="3">
-        <v>954900</v>
+        <v>988700</v>
       </c>
       <c r="I66" s="3">
-        <v>960100</v>
+        <v>994200</v>
       </c>
       <c r="J66" s="3">
-        <v>1133200</v>
+        <v>1173400</v>
       </c>
       <c r="K66" s="3">
         <v>1161600</v>
@@ -4476,25 +4476,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>375400</v>
+        <v>388800</v>
       </c>
       <c r="E72" s="3">
-        <v>99200</v>
+        <v>102700</v>
       </c>
       <c r="F72" s="3">
-        <v>-67100</v>
+        <v>-69500</v>
       </c>
       <c r="G72" s="3">
-        <v>-157500</v>
+        <v>-163100</v>
       </c>
       <c r="H72" s="3">
-        <v>-24200</v>
+        <v>-25100</v>
       </c>
       <c r="I72" s="3">
-        <v>-96500</v>
+        <v>-100000</v>
       </c>
       <c r="J72" s="3">
-        <v>-173200</v>
+        <v>-179300</v>
       </c>
       <c r="K72" s="3">
         <v>-521200</v>
@@ -4736,25 +4736,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2167700</v>
+        <v>2244600</v>
       </c>
       <c r="E76" s="3">
-        <v>1891500</v>
+        <v>1958600</v>
       </c>
       <c r="F76" s="3">
-        <v>1725200</v>
+        <v>1786400</v>
       </c>
       <c r="G76" s="3">
-        <v>1634700</v>
+        <v>1692700</v>
       </c>
       <c r="H76" s="3">
-        <v>1768100</v>
+        <v>1830800</v>
       </c>
       <c r="I76" s="3">
-        <v>1695700</v>
+        <v>1755900</v>
       </c>
       <c r="J76" s="3">
-        <v>1619200</v>
+        <v>1676600</v>
       </c>
       <c r="K76" s="3">
         <v>1273300</v>
@@ -4936,25 +4936,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>322200</v>
+        <v>333600</v>
       </c>
       <c r="E81" s="3">
-        <v>162200</v>
+        <v>168000</v>
       </c>
       <c r="F81" s="3">
-        <v>100100</v>
+        <v>103600</v>
       </c>
       <c r="G81" s="3">
-        <v>-132700</v>
+        <v>-137400</v>
       </c>
       <c r="H81" s="3">
-        <v>75500</v>
+        <v>78200</v>
       </c>
       <c r="I81" s="3">
-        <v>-38000</v>
+        <v>-39300</v>
       </c>
       <c r="J81" s="3">
-        <v>248900</v>
+        <v>257700</v>
       </c>
       <c r="K81" s="3">
         <v>-120400</v>
@@ -5416,25 +5416,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>380700</v>
+        <v>394200</v>
       </c>
       <c r="E89" s="3">
-        <v>374600</v>
+        <v>387900</v>
       </c>
       <c r="F89" s="3">
-        <v>166800</v>
+        <v>172700</v>
       </c>
       <c r="G89" s="3">
-        <v>-1456100</v>
+        <v>-1507800</v>
       </c>
       <c r="H89" s="3">
-        <v>1832900</v>
+        <v>1897900</v>
       </c>
       <c r="I89" s="3">
-        <v>185000</v>
+        <v>191600</v>
       </c>
       <c r="J89" s="3">
-        <v>314500</v>
+        <v>325600</v>
       </c>
       <c r="K89" s="3">
         <v>108400</v>
@@ -5701,25 +5701,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-202900</v>
+        <v>-210100</v>
       </c>
       <c r="E94" s="3">
-        <v>-213200</v>
+        <v>-220700</v>
       </c>
       <c r="F94" s="3">
-        <v>-363500</v>
+        <v>-376400</v>
       </c>
       <c r="G94" s="3">
-        <v>1465000</v>
+        <v>1516900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1802400</v>
+        <v>-1866300</v>
       </c>
       <c r="I94" s="3">
-        <v>-152000</v>
+        <v>-157400</v>
       </c>
       <c r="J94" s="3">
-        <v>-308600</v>
+        <v>-319500</v>
       </c>
       <c r="K94" s="3">
         <v>-72700</v>
@@ -5791,19 +5791,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-26400</v>
+        <v>-27400</v>
       </c>
       <c r="E96" s="3">
         <v>-500</v>
       </c>
       <c r="F96" s="3">
-        <v>-7900</v>
+        <v>-8200</v>
       </c>
       <c r="G96" s="3">
-        <v>-14000</v>
+        <v>-14500</v>
       </c>
       <c r="H96" s="3">
-        <v>-9400</v>
+        <v>-9700</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -6051,25 +6051,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-149300</v>
+        <v>-154600</v>
       </c>
       <c r="E100" s="3">
-        <v>-116000</v>
+        <v>-120100</v>
       </c>
       <c r="F100" s="3">
-        <v>180900</v>
+        <v>187400</v>
       </c>
       <c r="G100" s="3">
-        <v>-38600</v>
+        <v>-40000</v>
       </c>
       <c r="H100" s="3">
-        <v>-24100</v>
+        <v>-24900</v>
       </c>
       <c r="I100" s="3">
-        <v>-116200</v>
+        <v>-120300</v>
       </c>
       <c r="J100" s="3">
-        <v>-117800</v>
+        <v>-121900</v>
       </c>
       <c r="K100" s="3">
         <v>250100</v>
@@ -6116,25 +6116,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E101" s="3">
-        <v>-8900</v>
+        <v>-9200</v>
       </c>
       <c r="F101" s="3">
         <v>2000</v>
       </c>
       <c r="G101" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H101" s="3">
         <v>100</v>
       </c>
       <c r="I101" s="3">
-        <v>7100</v>
+        <v>7400</v>
       </c>
       <c r="J101" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="K101" s="3">
         <v>-7500</v>
@@ -6181,25 +6181,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>31000</v>
+        <v>32100</v>
       </c>
       <c r="E102" s="3">
-        <v>36600</v>
+        <v>37900</v>
       </c>
       <c r="F102" s="3">
-        <v>-13800</v>
+        <v>-14300</v>
       </c>
       <c r="G102" s="3">
-        <v>-26800</v>
+        <v>-27700</v>
       </c>
       <c r="H102" s="3">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="I102" s="3">
-        <v>-76100</v>
+        <v>-78800</v>
       </c>
       <c r="J102" s="3">
-        <v>-116500</v>
+        <v>-120600</v>
       </c>
       <c r="K102" s="3">
         <v>278200</v>

--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>HMY</t>
   </si>
@@ -656,18 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -678,283 +677,309 @@
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42369</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42277</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42185</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1770200</v>
+        <v>820700</v>
       </c>
       <c r="E8" s="3">
-        <v>1466000</v>
+        <v>793000</v>
       </c>
       <c r="F8" s="3">
-        <v>1310600</v>
+        <v>858700</v>
       </c>
       <c r="G8" s="3">
-        <v>1166100</v>
+        <v>832500</v>
       </c>
       <c r="H8" s="3">
-        <v>1236900</v>
+        <v>690600</v>
       </c>
       <c r="I8" s="3">
+        <v>734300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>684000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1135200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1216500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>750100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>843200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>755500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>822800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>655200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>649600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>616000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>585000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>646000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>596800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>293200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>273400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1281300</v>
+        <v>530100</v>
       </c>
       <c r="E9" s="3">
-        <v>1112200</v>
+        <v>512300</v>
       </c>
       <c r="F9" s="3">
-        <v>1113900</v>
+        <v>556500</v>
       </c>
       <c r="G9" s="3">
-        <v>1041600</v>
+        <v>539500</v>
       </c>
       <c r="H9" s="3">
-        <v>1069400</v>
+        <v>463600</v>
       </c>
       <c r="I9" s="3">
+        <v>492900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>529900</v>
+      </c>
+      <c r="K9" s="3">
         <v>972700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>948400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>675300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>734000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>689200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>761800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>583700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>567700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>579700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>533800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>524900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>547700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>289500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>270700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>488900</v>
+        <v>290600</v>
       </c>
       <c r="E10" s="3">
-        <v>353800</v>
+        <v>280800</v>
       </c>
       <c r="F10" s="3">
-        <v>196700</v>
+        <v>302300</v>
       </c>
       <c r="G10" s="3">
-        <v>124500</v>
+        <v>293100</v>
       </c>
       <c r="H10" s="3">
-        <v>167500</v>
+        <v>227000</v>
       </c>
       <c r="I10" s="3">
+        <v>241300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>154100</v>
+      </c>
+      <c r="K10" s="3">
         <v>162500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>268100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>74700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>109200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>66300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>61000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>71600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>81900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>36300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>51200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>121100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>49100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -978,73 +1003,81 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>32300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>19600</v>
-      </c>
-      <c r="F12" s="3">
-        <v>8900</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="L12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S12" s="3">
         <v>6400</v>
       </c>
-      <c r="H12" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>6900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>4400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>4300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>6400</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>8500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>5900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>7100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>3100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1108,96 +1141,108 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3100</v>
+        <v>88500</v>
       </c>
       <c r="E14" s="3">
-        <v>-35600</v>
+        <v>85500</v>
       </c>
       <c r="F14" s="3">
-        <v>39000</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="3">
-        <v>237400</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="3">
-        <v>15400</v>
+        <v>4800</v>
       </c>
       <c r="I14" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>20400</v>
+      </c>
+      <c r="K14" s="3">
         <v>126700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-2300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>225400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>9700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>329500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>13900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>114400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-45900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-1400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>249300</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>59800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>65100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>63100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>45300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>48100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>51400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1238,8 +1283,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1260,138 +1311,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1343700</v>
+        <v>631200</v>
       </c>
       <c r="E17" s="3">
-        <v>1216200</v>
+        <v>609900</v>
       </c>
       <c r="F17" s="3">
-        <v>1172800</v>
+        <v>654800</v>
       </c>
       <c r="G17" s="3">
-        <v>1302800</v>
+        <v>634800</v>
       </c>
       <c r="H17" s="3">
-        <v>1142800</v>
+        <v>563300</v>
       </c>
       <c r="I17" s="3">
+        <v>598900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>592600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1133900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>896000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>861100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>754200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>911200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>813500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1021500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>573700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>758500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>466400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>513000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>623000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>330900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>535400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>426500</v>
+        <v>189500</v>
       </c>
       <c r="E18" s="3">
-        <v>249800</v>
+        <v>183100</v>
       </c>
       <c r="F18" s="3">
-        <v>137900</v>
+        <v>203900</v>
       </c>
       <c r="G18" s="3">
-        <v>-136600</v>
+        <v>197700</v>
       </c>
       <c r="H18" s="3">
-        <v>94100</v>
+        <v>127300</v>
       </c>
       <c r="I18" s="3">
+        <v>135400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>91400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>320500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-111000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>89000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-155700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>9300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-366200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>75900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-142500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>118600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>133000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-26300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-37700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-262000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1415,167 +1480,181 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-3000</v>
+        <v>2900</v>
       </c>
       <c r="E20" s="3">
-        <v>-10600</v>
+        <v>2800</v>
       </c>
       <c r="F20" s="3">
-        <v>-4800</v>
+        <v>-5400</v>
       </c>
       <c r="G20" s="3">
-        <v>-8600</v>
+        <v>-5300</v>
       </c>
       <c r="H20" s="3">
-        <v>2500</v>
+        <v>20300</v>
       </c>
       <c r="I20" s="3">
+        <v>21600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-12700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-7900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-9500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-7600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>6700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>557700</v>
+        <v>248500</v>
       </c>
       <c r="E21" s="3">
-        <v>236700</v>
+        <v>240100</v>
       </c>
       <c r="F21" s="3">
-        <v>231600</v>
+        <v>274500</v>
       </c>
       <c r="G21" s="3">
-        <v>-141700</v>
+        <v>266100</v>
       </c>
       <c r="H21" s="3">
-        <v>198600</v>
+        <v>152300</v>
       </c>
       <c r="I21" s="3">
+        <v>161900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>144300</v>
+      </c>
+      <c r="K21" s="3">
         <v>2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>428300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-126800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>186000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-165600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>128200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-365400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>165000</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>45400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-222400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
+      <c r="D22" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F22" s="3">
+        <v>12100</v>
       </c>
       <c r="G22" s="3">
-        <v>6600</v>
+        <v>11700</v>
       </c>
       <c r="H22" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
+        <v>-1100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>-1100</v>
       </c>
       <c r="J22" s="3">
-        <v>7300</v>
+        <v>12100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>16</v>
+      <c r="L22" s="3">
+        <v>7300</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>16</v>
@@ -1583,11 +1662,11 @@
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1610,138 +1689,156 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>423500</v>
+        <v>116500</v>
       </c>
       <c r="E23" s="3">
-        <v>239200</v>
+        <v>112600</v>
       </c>
       <c r="F23" s="3">
-        <v>133000</v>
+        <v>205500</v>
       </c>
       <c r="G23" s="3">
-        <v>-151900</v>
+        <v>199200</v>
       </c>
       <c r="H23" s="3">
-        <v>92300</v>
+        <v>112700</v>
       </c>
       <c r="I23" s="3">
+        <v>119800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>69400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-11400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>318600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-113500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>81100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-165200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-369400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>82600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-141700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>119300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>134500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-29000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-39200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-263000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>87700</v>
+        <v>41800</v>
       </c>
       <c r="E24" s="3">
-        <v>68900</v>
+        <v>40400</v>
       </c>
       <c r="F24" s="3">
-        <v>28200</v>
+        <v>42500</v>
       </c>
       <c r="G24" s="3">
-        <v>-15800</v>
+        <v>41200</v>
       </c>
       <c r="H24" s="3">
-        <v>13200</v>
+        <v>32500</v>
       </c>
       <c r="I24" s="3">
+        <v>34500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K24" s="3">
         <v>27400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>59400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>5300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>8600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-36700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>23600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-64500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>28100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>40900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-39800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1805,138 +1902,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>335800</v>
+        <v>74700</v>
       </c>
       <c r="E26" s="3">
-        <v>170300</v>
+        <v>72200</v>
       </c>
       <c r="F26" s="3">
-        <v>104900</v>
+        <v>162900</v>
       </c>
       <c r="G26" s="3">
-        <v>-136100</v>
+        <v>157900</v>
       </c>
       <c r="H26" s="3">
-        <v>79100</v>
+        <v>80200</v>
       </c>
       <c r="I26" s="3">
+        <v>85300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>54700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-38800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>259200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-118900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>72600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-154400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-332700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>59000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-77200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>91200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>93500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-30500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-36900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-223200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>333600</v>
+        <v>73000</v>
       </c>
       <c r="E27" s="3">
-        <v>168000</v>
+        <v>70600</v>
       </c>
       <c r="F27" s="3">
-        <v>103600</v>
+        <v>161800</v>
       </c>
       <c r="G27" s="3">
-        <v>-137400</v>
+        <v>156900</v>
       </c>
       <c r="H27" s="3">
-        <v>78200</v>
+        <v>79100</v>
       </c>
       <c r="I27" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-39300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>257700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-120400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>72600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-154400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-332700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>59000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-77200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>91200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>93500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-30500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-36900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-223200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2000,8 +2115,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2065,8 +2186,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2130,8 +2257,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2195,138 +2328,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3000</v>
+        <v>-2900</v>
       </c>
       <c r="E32" s="3">
-        <v>10600</v>
+        <v>-2800</v>
       </c>
       <c r="F32" s="3">
-        <v>4800</v>
+        <v>5400</v>
       </c>
       <c r="G32" s="3">
-        <v>8600</v>
+        <v>5300</v>
       </c>
       <c r="H32" s="3">
-        <v>-2500</v>
+        <v>-20300</v>
       </c>
       <c r="I32" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>12700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>7900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>9500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>7600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>333600</v>
+        <v>73000</v>
       </c>
       <c r="E33" s="3">
-        <v>168000</v>
+        <v>70600</v>
       </c>
       <c r="F33" s="3">
-        <v>103600</v>
+        <v>161800</v>
       </c>
       <c r="G33" s="3">
-        <v>-137400</v>
+        <v>156900</v>
       </c>
       <c r="H33" s="3">
-        <v>78200</v>
+        <v>79100</v>
       </c>
       <c r="I33" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-39300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>257700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-120400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>72600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-154400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-332700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>59000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-77200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>91200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>93500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-30500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-36900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-223200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2390,143 +2541,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>333600</v>
+        <v>73000</v>
       </c>
       <c r="E35" s="3">
-        <v>168000</v>
+        <v>70600</v>
       </c>
       <c r="F35" s="3">
-        <v>103600</v>
+        <v>161800</v>
       </c>
       <c r="G35" s="3">
-        <v>-137400</v>
+        <v>156900</v>
       </c>
       <c r="H35" s="3">
-        <v>78200</v>
+        <v>79100</v>
       </c>
       <c r="I35" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-39300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>257700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-120400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>72600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-154400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-332700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>59000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-77200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>91200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>93500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-30500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-36900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-223200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42369</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42277</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42185</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2550,8 +2719,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2575,73 +2746,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>193600</v>
+        <v>257100</v>
       </c>
       <c r="E41" s="3">
-        <v>161600</v>
+        <v>248400</v>
       </c>
       <c r="F41" s="3">
-        <v>123700</v>
+        <v>187800</v>
       </c>
       <c r="G41" s="3">
-        <v>137900</v>
+        <v>182100</v>
       </c>
       <c r="H41" s="3">
-        <v>165700</v>
+        <v>152200</v>
       </c>
       <c r="I41" s="3">
+        <v>161800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>129100</v>
+      </c>
+      <c r="K41" s="3">
         <v>158900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>237600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>346300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>68100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>57200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>82800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>43700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>69400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>81700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>72000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>84300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>60000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>105300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>75600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2705,463 +2884,511 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>185200</v>
+        <v>123200</v>
       </c>
       <c r="E43" s="3">
-        <v>135000</v>
+        <v>119000</v>
       </c>
       <c r="F43" s="3">
-        <v>131100</v>
+        <v>179700</v>
       </c>
       <c r="G43" s="3">
-        <v>94800</v>
+        <v>174200</v>
       </c>
       <c r="H43" s="3">
-        <v>106200</v>
+        <v>117100</v>
       </c>
       <c r="I43" s="3">
+        <v>124500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K43" s="3">
         <v>93100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>83700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>71300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>71400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>61300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>70900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>70600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>65300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>65800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>48600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>44300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>45900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>55400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>55000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>181100</v>
+        <v>197400</v>
       </c>
       <c r="E44" s="3">
-        <v>184000</v>
+        <v>190700</v>
       </c>
       <c r="F44" s="3">
-        <v>154600</v>
+        <v>175700</v>
       </c>
       <c r="G44" s="3">
-        <v>158800</v>
+        <v>170300</v>
       </c>
       <c r="H44" s="3">
-        <v>125700</v>
+        <v>173300</v>
       </c>
       <c r="I44" s="3">
+        <v>184300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>161400</v>
+      </c>
+      <c r="K44" s="3">
         <v>143200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>123900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>131900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>106400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>113200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>107100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>109000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>90100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>73900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>95800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>78300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>86400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>89400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>91500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15900</v>
+        <v>30600</v>
       </c>
       <c r="E45" s="3">
-        <v>8500</v>
+        <v>29500</v>
       </c>
       <c r="F45" s="3">
-        <v>20600</v>
+        <v>13200</v>
       </c>
       <c r="G45" s="3">
-        <v>30800</v>
+        <v>12800</v>
       </c>
       <c r="H45" s="3">
-        <v>37500</v>
+        <v>5800</v>
       </c>
       <c r="I45" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K45" s="3">
         <v>86700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>44500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>32200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>20300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>14700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>35700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>107300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>102200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>90800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>25900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>1100</v>
       </c>
       <c r="V45" s="3">
         <v>1100</v>
       </c>
       <c r="W45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>575800</v>
+        <v>629800</v>
       </c>
       <c r="E46" s="3">
-        <v>489000</v>
+        <v>608600</v>
       </c>
       <c r="F46" s="3">
-        <v>430100</v>
+        <v>558600</v>
       </c>
       <c r="G46" s="3">
-        <v>422300</v>
+        <v>541600</v>
       </c>
       <c r="H46" s="3">
-        <v>435000</v>
+        <v>460700</v>
       </c>
       <c r="I46" s="3">
+        <v>489900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>449200</v>
+      </c>
+      <c r="K46" s="3">
         <v>481800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>489700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>553800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>278100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>252000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>275600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>259000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>332100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>323500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>307200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>232800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>193400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>251300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>223200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>24300</v>
+        <v>13900</v>
       </c>
       <c r="E47" s="3">
-        <v>25000</v>
+        <v>13400</v>
       </c>
       <c r="F47" s="3">
-        <v>25000</v>
+        <v>6600</v>
       </c>
       <c r="G47" s="3">
-        <v>28100</v>
+        <v>6400</v>
       </c>
       <c r="H47" s="3">
-        <v>25100</v>
+        <v>10000</v>
       </c>
       <c r="I47" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K47" s="3">
         <v>25800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>32600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>25800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>25600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>39000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>21600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>21300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>15400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>11900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2395200</v>
+        <v>2265000</v>
       </c>
       <c r="E48" s="3">
-        <v>2338900</v>
+        <v>2188700</v>
       </c>
       <c r="F48" s="3">
-        <v>2158700</v>
+        <v>2323800</v>
       </c>
       <c r="G48" s="3">
-        <v>1852300</v>
+        <v>2252900</v>
       </c>
       <c r="H48" s="3">
-        <v>2015100</v>
+        <v>2203700</v>
       </c>
       <c r="I48" s="3">
+        <v>2343000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2289700</v>
+      </c>
+      <c r="K48" s="3">
         <v>1893200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1949600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1590100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1536800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1597500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1876300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1920500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2036200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1969700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1816300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2007600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2063100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2111000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2092600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>192100</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I49" s="3">
         <v>1900</v>
       </c>
-      <c r="F49" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H49" s="3">
-        <v>19700</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K49" s="3">
         <v>20600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>30500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>29200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>29100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>30700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>30700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>31900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>39500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>39500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>51200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>58400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>60200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>62500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>62700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3225,8 +3452,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3290,73 +3523,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>372200</v>
+        <v>390400</v>
       </c>
       <c r="E52" s="3">
-        <v>370700</v>
+        <v>377300</v>
       </c>
       <c r="F52" s="3">
-        <v>354800</v>
+        <v>371200</v>
       </c>
       <c r="G52" s="3">
-        <v>332200</v>
+        <v>359900</v>
       </c>
       <c r="H52" s="3">
-        <v>324600</v>
+        <v>346600</v>
       </c>
       <c r="I52" s="3">
+        <v>368500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>380000</v>
+      </c>
+      <c r="K52" s="3">
         <v>328600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>357900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>232600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>203300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>209200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>215600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>215500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>209700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>201000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>197000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>174100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>173100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>176800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>174800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3420,73 +3665,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3368900</v>
+        <v>3312000</v>
       </c>
       <c r="E54" s="3">
-        <v>3225500</v>
+        <v>3200300</v>
       </c>
       <c r="F54" s="3">
-        <v>2970800</v>
+        <v>3268500</v>
       </c>
       <c r="G54" s="3">
-        <v>2637600</v>
+        <v>3168800</v>
       </c>
       <c r="H54" s="3">
-        <v>2819500</v>
+        <v>3038900</v>
       </c>
       <c r="I54" s="3">
+        <v>3231100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3137700</v>
+      </c>
+      <c r="K54" s="3">
         <v>2750000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2850000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2434800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2073200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2114900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2421700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2448400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2638800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2549200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2382900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2484700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2495800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2607500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2559200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>230400</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3510,8 +3767,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3535,194 +3794,208 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>290800</v>
+        <v>62300</v>
       </c>
       <c r="E57" s="3">
-        <v>295200</v>
+        <v>60200</v>
       </c>
       <c r="F57" s="3">
-        <v>258500</v>
+        <v>282200</v>
       </c>
       <c r="G57" s="3">
-        <v>253200</v>
+        <v>273500</v>
       </c>
       <c r="H57" s="3">
-        <v>236500</v>
+        <v>64000</v>
       </c>
       <c r="I57" s="3">
+        <v>68000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>269800</v>
+      </c>
+      <c r="K57" s="3">
         <v>247300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>221100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>163800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>159400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>165500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>175800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>167500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>148500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>131800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>125100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>113500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>112500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>129600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>117600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>21100</v>
+        <v>16900</v>
       </c>
       <c r="I58" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>21800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>22000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>13900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>42700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>120200</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>20100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>20500</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>64900</v>
+        <v>208500</v>
       </c>
       <c r="E59" s="3">
-        <v>86000</v>
+        <v>201500</v>
       </c>
       <c r="F59" s="3">
-        <v>25300</v>
+        <v>62900</v>
       </c>
       <c r="G59" s="3">
-        <v>25700</v>
+        <v>61000</v>
       </c>
       <c r="H59" s="3">
-        <v>33400</v>
+        <v>175800</v>
       </c>
       <c r="I59" s="3">
+        <v>187000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K59" s="3">
         <v>43800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>123500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>234200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>38500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>18100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>100</v>
-      </c>
-      <c r="U59" s="3">
-        <v>100</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
@@ -3730,203 +4003,227 @@
       <c r="W59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>356500</v>
+        <v>403100</v>
       </c>
       <c r="E60" s="3">
-        <v>387000</v>
+        <v>389500</v>
       </c>
       <c r="F60" s="3">
-        <v>283800</v>
+        <v>345800</v>
       </c>
       <c r="G60" s="3">
-        <v>280300</v>
+        <v>335300</v>
       </c>
       <c r="H60" s="3">
-        <v>291000</v>
+        <v>364600</v>
       </c>
       <c r="I60" s="3">
+        <v>387600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>296200</v>
+      </c>
+      <c r="K60" s="3">
         <v>312900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>366600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>411900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>202500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>186200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>199400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>223000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>150200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>252000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>129000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>136300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>133100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>129700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>117600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>188700</v>
+        <v>111300</v>
       </c>
       <c r="E61" s="3">
-        <v>315100</v>
+        <v>107500</v>
       </c>
       <c r="F61" s="3">
-        <v>389100</v>
+        <v>198900</v>
       </c>
       <c r="G61" s="3">
-        <v>179200</v>
+        <v>192900</v>
       </c>
       <c r="H61" s="3">
-        <v>179100</v>
+        <v>313300</v>
       </c>
       <c r="I61" s="3">
+        <v>333200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>406100</v>
+      </c>
+      <c r="K61" s="3">
         <v>167600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>248300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>406600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>297100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>335400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>350300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>305000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>168800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>19600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>89200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>136800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>211900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>292400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>240700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>571200</v>
+        <v>376900</v>
       </c>
       <c r="E62" s="3">
-        <v>557900</v>
+        <v>364200</v>
       </c>
       <c r="F62" s="3">
-        <v>506500</v>
+        <v>386600</v>
       </c>
       <c r="G62" s="3">
-        <v>481000</v>
+        <v>374800</v>
       </c>
       <c r="H62" s="3">
-        <v>515000</v>
+        <v>367800</v>
       </c>
       <c r="I62" s="3">
+        <v>391100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>413100</v>
+      </c>
+      <c r="K62" s="3">
         <v>510600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>606000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>342900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>277400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>291400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>344900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>348000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>362800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>357200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>341500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>320800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>308500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>309400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>306200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>29200</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3990,8 +4287,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4055,8 +4358,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4120,73 +4429,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1124400</v>
+        <v>1068800</v>
       </c>
       <c r="E66" s="3">
-        <v>1266900</v>
+        <v>1032800</v>
       </c>
       <c r="F66" s="3">
-        <v>1184400</v>
+        <v>1083100</v>
       </c>
       <c r="G66" s="3">
-        <v>944900</v>
+        <v>1050000</v>
       </c>
       <c r="H66" s="3">
-        <v>988700</v>
+        <v>1187100</v>
       </c>
       <c r="I66" s="3">
+        <v>1262200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1267800</v>
+      </c>
+      <c r="K66" s="3">
         <v>994200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1173400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1161600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>776700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>813000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>894600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>876000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>681800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>628900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>559600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>593900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>653500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>731500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>664600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4210,8 +4531,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4275,8 +4598,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4340,8 +4669,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4405,8 +4740,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4470,73 +4811,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>388800</v>
+        <v>122600</v>
       </c>
       <c r="E72" s="3">
-        <v>102700</v>
+        <v>118500</v>
       </c>
       <c r="F72" s="3">
-        <v>-69500</v>
+        <v>27300</v>
       </c>
       <c r="G72" s="3">
-        <v>-163100</v>
+        <v>26500</v>
       </c>
       <c r="H72" s="3">
-        <v>-25100</v>
+        <v>-263100</v>
       </c>
       <c r="I72" s="3">
+        <v>-279700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-466700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-100000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-179300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-521200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-313500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-399400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-236200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-245200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>92900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>62600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>143600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-10500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-99000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-129900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-111300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4600,8 +4953,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4665,8 +5024,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4730,73 +5095,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2244600</v>
+        <v>2233600</v>
       </c>
       <c r="E76" s="3">
-        <v>1958600</v>
+        <v>2158300</v>
       </c>
       <c r="F76" s="3">
-        <v>1786400</v>
+        <v>2177700</v>
       </c>
       <c r="G76" s="3">
-        <v>1692700</v>
+        <v>2111300</v>
       </c>
       <c r="H76" s="3">
-        <v>1830800</v>
+        <v>1845300</v>
       </c>
       <c r="I76" s="3">
+        <v>1962000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1864600</v>
+      </c>
+      <c r="K76" s="3">
         <v>1755900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1676600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1273300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1296500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1301900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1527100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1572400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1957000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1920300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1823300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1890800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1842300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1876000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1894600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4860,143 +5237,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42369</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42277</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42185</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>333600</v>
+        <v>73000</v>
       </c>
       <c r="E81" s="3">
-        <v>168000</v>
+        <v>70600</v>
       </c>
       <c r="F81" s="3">
-        <v>103600</v>
+        <v>161800</v>
       </c>
       <c r="G81" s="3">
-        <v>-137400</v>
+        <v>156900</v>
       </c>
       <c r="H81" s="3">
-        <v>78200</v>
+        <v>79100</v>
       </c>
       <c r="I81" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-39300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>257700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-120400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>72600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-154400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-332700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>59000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-77200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>91200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>93500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-30500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-36900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-223200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5020,31 +5415,33 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>45300</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>48100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>51400</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>57200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>56700</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5085,8 +5482,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5150,8 +5553,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5215,8 +5624,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5280,8 +5695,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5345,8 +5766,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5410,73 +5837,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>394200</v>
+        <v>237100</v>
       </c>
       <c r="E89" s="3">
-        <v>387900</v>
+        <v>229100</v>
       </c>
       <c r="F89" s="3">
-        <v>172700</v>
+        <v>191200</v>
       </c>
       <c r="G89" s="3">
-        <v>-1507800</v>
+        <v>185400</v>
       </c>
       <c r="H89" s="3">
-        <v>1897900</v>
+        <v>182700</v>
       </c>
       <c r="I89" s="3">
+        <v>194300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>90100</v>
+      </c>
+      <c r="K89" s="3">
         <v>191600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>325600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>108400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>148900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>116800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>158100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>127100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>120500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>123900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>113500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>184600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>120800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>50900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>132800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5500,73 +5939,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3868000</v>
+        <v>-124100</v>
       </c>
       <c r="E91" s="3">
-        <v>-3994000</v>
+        <v>-119900</v>
       </c>
       <c r="F91" s="3">
-        <v>-3646000</v>
+        <v>-105700</v>
       </c>
       <c r="G91" s="3">
-        <v>-3044000</v>
+        <v>-102500</v>
       </c>
       <c r="H91" s="3">
-        <v>-3170000</v>
+        <v>-106000</v>
       </c>
       <c r="I91" s="3">
+        <v>-112700</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-107200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2776000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2366000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1340000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2270000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-151700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-143200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-123700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-168700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-161000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-85000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-84900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-80100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-42100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-187500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5630,8 +6077,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5695,73 +6148,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-210100</v>
+        <v>-126900</v>
       </c>
       <c r="E94" s="3">
-        <v>-220700</v>
+        <v>-122600</v>
       </c>
       <c r="F94" s="3">
-        <v>-376400</v>
+        <v>-101900</v>
       </c>
       <c r="G94" s="3">
-        <v>1516900</v>
+        <v>-98800</v>
       </c>
       <c r="H94" s="3">
-        <v>-1866300</v>
+        <v>-104000</v>
       </c>
       <c r="I94" s="3">
+        <v>-110600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-196400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-157400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-319500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-72700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-121100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-141400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-139700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-340200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-170000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-158300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-57400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-96200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-79800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-42300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-192100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5785,62 +6250,64 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-27400</v>
+        <v>25400</v>
       </c>
       <c r="E96" s="3">
-        <v>-500</v>
+        <v>24600</v>
       </c>
       <c r="F96" s="3">
-        <v>-8200</v>
+        <v>12700</v>
       </c>
       <c r="G96" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="S96" s="3">
         <v>-14500</v>
       </c>
-      <c r="H96" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-12900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -5850,8 +6317,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5915,8 +6388,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5980,8 +6459,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6045,199 +6530,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-154600</v>
+        <v>-73700</v>
       </c>
       <c r="E100" s="3">
-        <v>-120100</v>
+        <v>-71200</v>
       </c>
       <c r="F100" s="3">
-        <v>187400</v>
+        <v>-75000</v>
       </c>
       <c r="G100" s="3">
-        <v>-40000</v>
+        <v>-72700</v>
       </c>
       <c r="H100" s="3">
-        <v>-24900</v>
+        <v>-56600</v>
       </c>
       <c r="I100" s="3">
+        <v>-60100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>97800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-120300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-121900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>250100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-15500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>20900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>196300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>36500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>31300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-55000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-62300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-56000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>21200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>12900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2600</v>
+        <v>-4300</v>
       </c>
       <c r="E101" s="3">
-        <v>-9200</v>
+        <v>-4600</v>
       </c>
       <c r="F101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>200</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="R101" s="3">
+        <v>400</v>
+      </c>
+      <c r="S101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V101" s="3">
         <v>2000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="P101" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>5100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>500</v>
       </c>
       <c r="W101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>32100</v>
+        <v>34400</v>
       </c>
       <c r="E102" s="3">
-        <v>37900</v>
+        <v>33300</v>
       </c>
       <c r="F102" s="3">
-        <v>-14300</v>
+        <v>15600</v>
       </c>
       <c r="G102" s="3">
-        <v>-27700</v>
+        <v>15100</v>
       </c>
       <c r="H102" s="3">
-        <v>6800</v>
+        <v>17800</v>
       </c>
       <c r="I102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-78800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-120600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>278200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-22700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>40700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-21600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>25500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-13100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>29700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-45900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>HMY</t>
   </si>
@@ -656,19 +656,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -679,307 +678,333 @@
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42551</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42369</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42277</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42185</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>983500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1076200</v>
+      </c>
+      <c r="F8" s="3">
         <v>820700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>793000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>858700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>832500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>690600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>734300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>684000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1135200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1216500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>750100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>843200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>755500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>822800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>655200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>649600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>616000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>585000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>646000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>596800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>293200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>273400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>597400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>653700</v>
+      </c>
+      <c r="F9" s="3">
         <v>530100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>512300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>556500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>539500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>463600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>492900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>529900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>972700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>948400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>675300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>734000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>689200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>761800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>583700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>567700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>579700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>533800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>524900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>547700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>289500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>270700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>422500</v>
+      </c>
+      <c r="F10" s="3">
         <v>290600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>280800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>302300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>293100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>227000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>241300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>154100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>162500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>268100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>74700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>109200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>66300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>61000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>71600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>81900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>36300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>51200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>121100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>49100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1005,8 +1030,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,53 +1058,59 @@
       <c r="J12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="3">
         <v>5700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>6900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>4400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>5300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>6400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>5900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1147,109 +1180,121 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F14" s="3">
         <v>88500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>85500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>4800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>20400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>126700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-2300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>225400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>9700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>329500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>13900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>114400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-45900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-1400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>249300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>70400</v>
+      </c>
+      <c r="F15" s="3">
         <v>61900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>59800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>65100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>63100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>45300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>48100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>51400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1289,8 +1334,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1313,150 +1364,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>712500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>779700</v>
+      </c>
+      <c r="F17" s="3">
         <v>631200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>609900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>654800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>634800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>563300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>598900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>592600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1133900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>896000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>861100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>754200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>911200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>813500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1021500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>573700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>758500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>466400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>513000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>623000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>330900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>535400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>296600</v>
+      </c>
+      <c r="F18" s="3">
         <v>189500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>183100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>203900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>197700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>127300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>135400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>91400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>320500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-111000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>89000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-155700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>9300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-366200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>75900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-142500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>118600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>133000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-26300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-37700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-262000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1482,185 +1547,199 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-5300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>20300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>21600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-12700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-7900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>6700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>333700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>365200</v>
+      </c>
+      <c r="F21" s="3">
         <v>248500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>240100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>274500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>266100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>152300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>161900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>144300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>428300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-126800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>186000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-165600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>128200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-365400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>165000</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>45400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-222400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F22" s="3">
         <v>-6000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>-5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>12100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>11700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>-1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>-1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12100</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L22" s="3">
-        <v>7300</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
+      <c r="N22" s="3">
+        <v>7300</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>16</v>
@@ -1668,11 +1747,11 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1695,150 +1774,168 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>299900</v>
+      </c>
+      <c r="F23" s="3">
         <v>116500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>112600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>205500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>199200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>112700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>119800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>69400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-11400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>318600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-113500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>81100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-165200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-369400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>82600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-141700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>119300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>134500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-29000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-39200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-263000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>70100</v>
+      </c>
+      <c r="F24" s="3">
         <v>41800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>40400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>42500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>41200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>32500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>34500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>14700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>27400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>59400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>8600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-10800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-36700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>23600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-64500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>28100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>40900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1908,150 +2005,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>229800</v>
+      </c>
+      <c r="F26" s="3">
         <v>74700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>72200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>162900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>157900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>80200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>85300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>54700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-38800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>259200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-118900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>72600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-154400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-332700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>59000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-77200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>91200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>93500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-30500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-36900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-223200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>227700</v>
+      </c>
+      <c r="F27" s="3">
         <v>73000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>70600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>161800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>156900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>79100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>84100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>54100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-39300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>257700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-120400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>72600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-154400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-332700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>59000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-77200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>91200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>93500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-30500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-36900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-223200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2121,8 +2236,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2192,8 +2313,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2263,8 +2390,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2334,150 +2467,168 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>5300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-20300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-21600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>12700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>7900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>7600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-6700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>227700</v>
+      </c>
+      <c r="F33" s="3">
         <v>73000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>70600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>161800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>156900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>79100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>84100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>54100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-39300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>257700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-120400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>72600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-154400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-332700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>59000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-77200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>91200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>93500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-30500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-36900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-223200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2547,155 +2698,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>227700</v>
+      </c>
+      <c r="F35" s="3">
         <v>73000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>70600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>161800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>156900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>79100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>84100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>54100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-39300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>257700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-120400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>72600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-154400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-332700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>59000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-77200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>91200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>93500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-30500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-36900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-223200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42551</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42369</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42277</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42185</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2721,8 +2890,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2748,79 +2919,87 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>497600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>544500</v>
+      </c>
+      <c r="F41" s="3">
         <v>257100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>248400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>187800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>182100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>152200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>161800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>129100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>158900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>237600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>346300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>68100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>57200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>82800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>43700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>69400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>81700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>72000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>84300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>60000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>105300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>75600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2890,505 +3069,553 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>206700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>226200</v>
+      </c>
+      <c r="F43" s="3">
         <v>123200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>119000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>179700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>174200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>117100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>124500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>137200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>93100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>83700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>71300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>71400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>61300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>70900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>70600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>65300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>65800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>48600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>44300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>45900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>55400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>55000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>204100</v>
+      </c>
+      <c r="F44" s="3">
         <v>197400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>190700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>175700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>170300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>173300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>184300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>161400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>143200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>123900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>131900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>106400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>113200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>107100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>109000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>90100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>73900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>95800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>78300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>86400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>89400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>91500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F45" s="3">
         <v>30600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>29500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>12800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>86700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>44500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>32200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>20300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>14700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>35700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>107300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>102200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>90800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>25900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1100</v>
       </c>
       <c r="X45" s="3">
         <v>1100</v>
       </c>
       <c r="Y45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>906600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>992100</v>
+      </c>
+      <c r="F46" s="3">
         <v>629800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>608600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>558600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>541600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>460700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>489900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>449200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>481800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>489700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>553800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>278100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>252000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>275600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>259000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>332100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>323500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>307200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>232800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>193400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>251300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>223200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F47" s="3">
         <v>13900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>13400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>6600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>6400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>10000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>10700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>25800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>32600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>29100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>25800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>25600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>39000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>21600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>21300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>15400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>11300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>11900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>6000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2330400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2550100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2265000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2188700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2323800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2252900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2203700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2343000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2289700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1893200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1949600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1590100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1536800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1597500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1876300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1920500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2036200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1969700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1816300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2007600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2063100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2111000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2092600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>192100</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>700</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>30500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>29200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>29100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>30700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>30700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>31900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>39500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>39500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>51200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>58400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>60200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>62500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>62700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3458,8 +3685,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3529,79 +3762,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>432200</v>
+      </c>
+      <c r="F52" s="3">
         <v>390400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>377300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>371200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>359900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>346600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>368500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>380000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>328600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>357900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>232600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>203300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>209200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>215600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>215500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>209700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>201000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>197000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>174100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>173100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>176800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>174800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3671,79 +3916,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3648800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3992800</v>
+      </c>
+      <c r="F54" s="3">
         <v>3312000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3200300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3268500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3168800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3038900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3231100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3137700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2750000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2850000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2434800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2073200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2114900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2421700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2448400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2638800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2549200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2382900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2484700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2495800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2607500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2559200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>230400</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3769,8 +4026,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3796,212 +4055,226 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>301500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>329900</v>
+      </c>
+      <c r="F57" s="3">
         <v>62300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>60200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>282200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>273500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>64000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>68000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>269800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>247300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>221100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>163800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>159400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>165500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>175800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>167500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>148500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>131800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>125100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>113500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>112500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>129600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>117600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="3">
         <v>14700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>16900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>18000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>21800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>22000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>13900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>42700</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>120200</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>20100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>20500</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3" t="s">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>204600</v>
+      </c>
+      <c r="F59" s="3">
         <v>208500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>201500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>62900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>61000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>175800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>187000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>26400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>43800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>123500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>234200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>38500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>18100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>12700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3" t="s">
+      <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
@@ -4009,221 +4282,245 @@
       <c r="Y59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>539400</v>
+      </c>
+      <c r="F60" s="3">
         <v>403100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>389500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>345800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>335300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>364600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>387600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>296200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>312900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>366600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>411900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>202500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>186200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>199400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>223000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>150200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>252000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>129000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>136300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>133100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>129700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>117600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>135200</v>
+      </c>
+      <c r="F61" s="3">
         <v>111300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>107500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>198900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>192900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>313300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>333200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>406100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>167600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>248300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>406600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>297100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>335400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>350300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>305000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>168800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>19600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>89200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>136800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>211900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>292400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>240700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>466100</v>
+      </c>
+      <c r="F62" s="3">
         <v>376900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>364200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>386600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>374800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>367800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>391100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>413100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>510600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>606000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>342900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>277400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>291400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>344900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>348000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>362800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>357200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>341500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>320800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>308500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>309400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>306200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>29200</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4293,8 +4590,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4364,8 +4667,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4435,79 +4744,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1210300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1324400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1068800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1032800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1083100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1050000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1187100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1262200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1267800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>994200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1173400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1161600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>776700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>813000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>894600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>876000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>681800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>628900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>559600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>593900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>653500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>731500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>664600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4533,8 +4854,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4604,8 +4927,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4675,8 +5004,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4746,8 +5081,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4817,79 +5158,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>503000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>550400</v>
+      </c>
+      <c r="F72" s="3">
         <v>122600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>118500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>27300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>26500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-263100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-279700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-466700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-100000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-179300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-521200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-313500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-399400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-236200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-245200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>92900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>62600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>143600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-10500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-99000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-129900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-111300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4959,8 +5312,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5030,8 +5389,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5101,79 +5466,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2427000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2655800</v>
+      </c>
+      <c r="F76" s="3">
         <v>2233600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2158300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2177700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2111300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1845300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1962000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1864600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1755900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1676600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1273300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1296500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1301900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1527100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1572400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1957000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1920300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1823300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1890800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1842300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1876000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1894600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5243,155 +5620,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42551</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42369</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42277</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42185</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>227700</v>
+      </c>
+      <c r="F81" s="3">
         <v>73000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>70600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>161800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>156900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>79100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>84100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>54100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-39300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>257700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-120400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>72600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-154400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-332700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>59000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-77200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>91200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>93500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-30500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-36900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-223200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5417,38 +5812,40 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>63100</v>
+      </c>
+      <c r="F83" s="3">
         <v>45300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>48100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>51400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>48500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>57200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>64000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>56700</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5488,8 +5885,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5559,8 +5962,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5630,8 +6039,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5701,8 +6116,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5772,8 +6193,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5843,79 +6270,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>295100</v>
+      </c>
+      <c r="F89" s="3">
         <v>237100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>229100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>191200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>185400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>182700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>194300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>90100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>191600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>325600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>108400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>148900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>116800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>158100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>127100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>120500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>123900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>113500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>184600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>120800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>50900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>132800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5941,79 +6380,87 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-139300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-124100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-119900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-105700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-102500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-106000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-112700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-107200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2776000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2366000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1340000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2270000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-151700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-143200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-123700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-168700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-161000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-85000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-84900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-80100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-42100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-187500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6083,8 +6530,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6154,79 +6607,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-131600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-144000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-126900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-122600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-101900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-98800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-104000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-110600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-196400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-157400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-319500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-72700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-121100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-141400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-139700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-340200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-170000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-158300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-57400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-96200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-79800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-42300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-192100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6252,38 +6717,40 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F96" s="3">
         <v>25400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>24600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>12700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>12300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>4000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -6300,20 +6767,20 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-10100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-14500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-12900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -6323,8 +6790,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6394,8 +6867,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6465,8 +6944,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6536,217 +7021,241 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-73700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-71200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-75000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-72700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-56600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-60100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>97800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-120300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-121900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>250100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-15500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>20900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>196300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>36500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>31300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-55000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-62300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-56000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>21200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>12900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-4300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-4600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>7400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-7500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-4800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>5100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X101" s="3">
-        <v>500</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>136300</v>
+      </c>
+      <c r="F102" s="3">
         <v>34400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>33300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>15600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>17800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-78800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-120600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>278200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>14000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-22700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>40700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-21600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>25500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-13100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>29700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-45900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-4300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>HMY</t>
   </si>
@@ -656,22 +656,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -682,355 +681,381 @@
     <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42551</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42369</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42277</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1340800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1285200</v>
+      </c>
+      <c r="F8" s="3">
         <v>1035000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1000200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>983500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1076200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>820700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>793000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>858700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>832500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>690600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>734300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>684000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1135200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1216500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>750100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>843200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>755500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>822800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>655200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>649600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>616000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>585000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>646000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>596800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>293200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>273400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>719300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>689500</v>
+      </c>
+      <c r="F9" s="3">
         <v>620400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>599500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>597400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>653700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>530100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>512300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>556500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>539500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>463600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>492900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>529900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>972700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>948400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>675300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>734000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>689200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>761800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>583700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>567700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>579700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>533800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>524900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>547700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>289500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>270700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>621500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>595700</v>
+      </c>
+      <c r="F10" s="3">
         <v>414600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>400700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>386100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>422500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>290600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>280800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>302300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>293100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>227000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>241300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>154100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>162500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>268100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>74700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>109200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>66300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>61000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>71600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>81900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>36300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>51200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>121100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>49100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1060,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,53 +1125,59 @@
       <c r="N12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="3">
         <v>5700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>6900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>4400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>4300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>5300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>6400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>8500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>5900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>7100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>3000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>3100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1226,133 +1259,145 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F14" s="3">
         <v>31400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>30300</v>
       </c>
-      <c r="F14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>4200</v>
-      </c>
       <c r="H14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J14" s="3">
         <v>12000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>11600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>5100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>20400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>126700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>5200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>225400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>9700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>329500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>13900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>114400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-45900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>249300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F15" s="3">
         <v>68000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>65700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>64300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>70400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>138400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>133800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>65100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>63100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>45300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>48100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>51400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1392,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1420,174 +1471,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>893800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>856700</v>
+      </c>
+      <c r="F17" s="3">
         <v>727900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>703400</v>
       </c>
-      <c r="F17" s="3">
-        <v>712500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>779700</v>
-      </c>
       <c r="H17" s="3">
+        <v>704500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>770900</v>
+      </c>
+      <c r="J17" s="3">
         <v>707700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>683900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>654800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>634800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>563300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>598900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>592600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1133900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>896000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>861100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>754200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>911200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>813500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1021500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>573700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>758500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>466400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>513000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>623000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>330900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>535400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>428500</v>
+      </c>
+      <c r="F18" s="3">
         <v>307100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>296800</v>
       </c>
-      <c r="F18" s="3">
-        <v>271000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>296600</v>
-      </c>
       <c r="H18" s="3">
+        <v>279000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>305300</v>
+      </c>
+      <c r="J18" s="3">
         <v>113000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>109200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>203900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>197700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>127300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>135400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>91400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>320500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-111000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>89000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-155700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>9300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-366200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>75900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-142500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>118600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>133000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-37700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-262000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1617,221 +1682,235 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>20300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>21600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-12700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-7900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-9500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>6700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>541600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>519100</v>
+      </c>
+      <c r="F21" s="3">
         <v>375900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>363200</v>
       </c>
-      <c r="F21" s="3">
-        <v>333700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>365200</v>
-      </c>
       <c r="H21" s="3">
+        <v>341700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>373900</v>
+      </c>
+      <c r="J21" s="3">
         <v>248500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>240100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>274500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>266100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>152300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>161900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>144300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>428300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-126800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>186000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-165600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>128200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-365400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>165000</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>45400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-222400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F22" s="3">
         <v>-4900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>-4800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>8600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>9400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>-6000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>-5800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>11700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>-1100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>-1100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>12100</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P22" s="3">
-        <v>7300</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>16</v>
+      <c r="R22" s="3">
+        <v>7300</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -1839,11 +1918,11 @@
       <c r="T22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1866,174 +1945,192 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>410200</v>
+      </c>
+      <c r="F23" s="3">
         <v>305700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>295400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>274000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>299900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>116500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>112600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>205500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>199200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>112700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>119800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>69400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-11400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>318600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-113500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>81100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-165200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-369400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>82600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-141700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>119300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>134500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-39200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-263000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>125500</v>
+      </c>
+      <c r="F24" s="3">
         <v>119300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>115300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>64100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>70100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>41800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>40400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>42500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>41200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>32500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>34500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>14700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>27400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>59400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>8600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-10800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-36700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>23600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-64500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>28100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>40900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-39800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2115,174 +2212,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>296900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>284600</v>
+      </c>
+      <c r="F26" s="3">
         <v>186400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>180100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>210000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>229800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>74700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>72200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>162900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>157900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>80200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>85300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>54700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-38800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>259200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-118900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>72600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-154400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-332700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>59000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-77200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>91200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>93500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-223200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>282200</v>
+      </c>
+      <c r="F27" s="3">
         <v>183800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>177600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>208100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>227700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>73000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>70600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>161800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>156900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>79100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>84100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>54100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-39300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>257700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-120400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>72600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-154400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-332700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>59000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-77200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>91200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>93500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-223200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2364,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2447,8 +2568,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2530,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2613,174 +2746,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-20300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-21600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>12700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>7900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>9500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-6700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>282200</v>
+      </c>
+      <c r="F33" s="3">
         <v>183800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>177600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>208100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>227700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>73000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>70600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>161800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>156900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>79100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>84100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>54100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-39300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>257700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-120400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>72600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-154400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-332700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>59000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-77200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>91200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>93500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-223200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2862,179 +3013,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>282200</v>
+      </c>
+      <c r="F35" s="3">
         <v>183800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>177600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>208100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>227700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>73000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>70600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>161800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>156900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>79100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>84100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>54100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-39300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>257700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-120400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>72600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-154400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-332700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>59000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-77200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>91200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>93500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-223200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42551</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42369</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42277</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3064,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3095,91 +3266,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>443900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>425500</v>
+      </c>
+      <c r="F41" s="3">
         <v>737800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>713000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>497600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>544500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>257100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>248400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>187800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>182100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>152200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>161800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>129100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>158900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>237600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>346300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>68100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>57200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>82800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>43700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>69400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>81700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>72000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>84300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>60000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>105300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>75600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3261,589 +3440,637 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>227100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>217700</v>
+      </c>
+      <c r="F43" s="3">
         <v>200000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>193300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>206700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>226200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>123200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>119000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>179700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>174200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>117100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>124500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>137200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>93100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>83700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>71300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>71400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>61300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>70900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>70600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>65300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>65800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>48600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>44300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>45900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>55400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>55000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>293300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>281100</v>
+      </c>
+      <c r="F44" s="3">
         <v>215400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>208200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>186500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>204100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>197400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>190700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>175700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>170300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>173300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>184300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>161400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>143200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>123900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>131900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>106400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>113200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>107100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>109000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>90100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>73900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>95800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>78300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>86400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>89400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>91500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F45" s="3">
         <v>18700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>18100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>30600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>29500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>13200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>12800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>19500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>86700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>44500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>32200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>20300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>14700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>35700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>107300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>102200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>90800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>25900</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1100</v>
       </c>
       <c r="AB45" s="3">
         <v>1100</v>
       </c>
       <c r="AC45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>984300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>943500</v>
+      </c>
+      <c r="F46" s="3">
         <v>1199900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1159600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>906600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>992100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>629800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>608600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>558600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>541600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>460700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>489900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>449200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>481800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>489700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>553800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>278100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>252000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>275600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>259000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>332100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>323500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>307200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>232800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>193400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>251300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>223200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F47" s="3">
         <v>17100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>7400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>8100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>13900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>13400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>6600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>6400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>10700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>5900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>25800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>32600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>29100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>25800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>25600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>39000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>21600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>21300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>15400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>11300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>11900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>6100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>6000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>6000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5422200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5197400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2718400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2627100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2330400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2550100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2265000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2188700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2323800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2252900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2203700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2343000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2289700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1893200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1949600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1590100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1536800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1597500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1876300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1920500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2036200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1969700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1816300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2007600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2063100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2111000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2092600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>192100</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>20600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>30500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>29200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>29100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>30700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>30700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>31900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>39500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>39500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>51200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>58400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>60200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>62500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>62700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3925,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4008,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>491900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>471500</v>
+      </c>
+      <c r="F52" s="3">
         <v>420000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>405900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>395000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>432200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>390400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>377300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>371200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>359900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>346600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>368500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>380000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>328600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>357900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>232600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>203300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>209200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>215600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>215500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>209700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>201000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>197000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>174100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>173100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>176800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>174800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4174,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6923200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6636100</v>
+      </c>
+      <c r="F54" s="3">
         <v>4364700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4218100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3648800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3992800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3312000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3200300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3268500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3168800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3038900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3231100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3137700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2750000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2850000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2434800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2073200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2114900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2421700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2448400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2638800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2549200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2382900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2484700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2495800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2607500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2559200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>230400</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4288,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4319,248 +4578,262 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>515500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>494100</v>
+      </c>
+      <c r="F57" s="3">
         <v>82200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>79500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>301500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>329900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>62300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>60200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>282200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>273500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>64000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>68000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>269800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>247300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>221100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>163800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>159400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>165500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>175800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>167500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>148500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>131800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>125100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>113500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>112500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>129600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>117600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>680100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>651900</v>
+      </c>
+      <c r="F58" s="3">
         <v>14900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>14700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>14200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>16900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>18000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>21800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>22000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>13900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>42700</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>120200</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>20100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>20500</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3" t="s">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>620700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>595000</v>
+      </c>
+      <c r="F59" s="3">
         <v>458600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>443200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>187000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>204600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>208500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>201500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>62900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>61000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>175800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>187000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>26400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>43800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>123500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>234200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>38500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>15500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>18100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>12700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3" t="s">
+      <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>3900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>100</v>
       </c>
       <c r="AB59" s="3">
         <v>100</v>
@@ -4568,257 +4841,281 @@
       <c r="AC59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1816300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1741000</v>
+      </c>
+      <c r="F60" s="3">
         <v>697700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>674200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>493000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>539400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>403100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>389500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>345800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>335300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>364600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>387600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>296200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>312900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>366600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>411900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>202500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>186200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>199400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>223000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>150200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>252000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>129000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>136300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>133100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>129700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>117600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>117800</v>
+      </c>
+      <c r="F61" s="3">
         <v>119600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>115600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>123600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>135200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>111300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>107500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>198900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>192900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>313300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>333200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>406100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>167600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>248300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>406600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>297100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>335400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>350300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>305000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>168800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>19600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>89200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>136800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>211900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>292400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>240700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>815500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>781700</v>
+      </c>
+      <c r="F62" s="3">
         <v>563400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>544500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>425900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>466100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>376900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>364200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>386600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>374800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>367800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>391100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>413100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>510600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>606000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>342900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>277400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>291400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>344900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>348000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>362800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>357200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>341500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>320800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>308500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>309400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>306200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>29200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4900,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4983,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5066,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3770200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3613900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1632700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1577800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1210300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1324400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1068800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1032800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1083100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1050000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1187100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1262200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1267800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>994200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1173400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1161600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>776700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>813000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>894600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>876000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>681800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>628900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>559600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>593900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>653500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>731500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>664600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5180,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5263,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5346,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5429,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5512,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1410000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1351500</v>
+      </c>
+      <c r="F72" s="3">
         <v>821300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>793700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>503000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>550400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>122600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>118500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>27300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>26500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-263100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-279700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-466700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-100000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-179300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-521200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-313500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-399400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-236200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-245200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>92900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>62600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>143600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-129900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-111300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5678,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5761,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5844,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3133600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3003700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2716400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2625200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2427000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2655800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2233600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2158300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2177700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2111300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1845300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1962000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1864600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1755900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1676600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1273300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1296500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1301900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1527100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1572400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1957000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1920300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1823300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1890800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1842300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1876000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1894600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6010,179 +6387,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42551</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42369</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42277</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>282200</v>
+      </c>
+      <c r="F81" s="3">
         <v>183800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>177600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>208100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>227700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>73000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>70600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>161800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>156900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>79100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>84100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>54100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-39300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>257700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-120400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>72600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-154400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-332700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>59000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-77200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>91200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>93500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-223200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6212,50 +6607,52 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>70400</v>
+      </c>
+      <c r="F83" s="3">
         <v>61900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>59800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>65100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>63100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>45300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>48100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>51400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>48500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>57200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>64000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>56700</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -6295,8 +6692,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6378,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6461,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6544,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6627,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6710,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>418200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>400900</v>
+      </c>
+      <c r="F89" s="3">
         <v>350900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>339100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>269700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>295100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>237100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>229100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>191200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>185400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>182700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>194300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>90100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>191600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>325600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>108400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>148900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>116800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>158100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>127100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>120500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>123900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>113500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>184600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>120800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>50900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>132800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6824,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-245100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-198500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-191800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-127300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-139300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-124100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-119900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-105700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-102500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-106000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-112700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-107200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2776000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2366000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1340000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2270000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-151700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-143200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-123700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-168700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-161000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-85000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-84900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-80100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-187500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6990,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7073,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-798700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-765600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-196700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-190100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-131600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-144000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-126900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-122600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-101900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-98800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-104000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-110600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-196400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-157400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-319500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-72700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-121100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-141400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-139700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-340200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-170000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-158300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-57400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-96200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-42300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-192100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7187,50 +7652,52 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F96" s="3">
         <v>40600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>39200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>15800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>17300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>25400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>24600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>12700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>12300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>4000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7247,20 +7714,20 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-10100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-14500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7270,8 +7737,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7353,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7436,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7519,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>207800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>199200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-46800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-45300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-14600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-73700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-71200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-75000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-72700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-56600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-60100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>97800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-120300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-121900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>250100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-15500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>20900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>196300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>36500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>31300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-62300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>21200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>12900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>7400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-7500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-4800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>5100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>500</v>
       </c>
       <c r="AC101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-173700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-166500</v>
+      </c>
+      <c r="F102" s="3">
         <v>104300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>100800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>124500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>136300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>34400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>33300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>15100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>17800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-7400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-78800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-120600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>278200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>14000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-22700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>40700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-21600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-12600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>25500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>29700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-45900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-4300</v>
       </c>
     </row>
